--- a/.trash/易畫165與ASCII94.xlsx
+++ b/.trash/易畫165與ASCII94.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\share\git\rime-jek\.trash\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B69B784-A83C-4141-BAF9-25AFC67C1F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E691509-064E-4CEE-947D-2666F1DD8FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{B55F1E0F-6405-49D3-ACBC-C1F7C0B264EC}"/>
   </bookViews>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="1124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="1126">
   <si>
     <t>268A</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3735,6 +3735,14 @@
   </si>
   <si>
     <t>𝌂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>𝌂𝌁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>𝍂</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -13590,7 +13598,7 @@
         <v>1121</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>1122</v>
@@ -13599,6 +13607,9 @@
         <f>DEC2HEX(_xlfn.UNICODE(K21))</f>
         <v>1D301</v>
       </c>
+      <c r="M21" s="2" t="s">
+        <v>1124</v>
+      </c>
     </row>
     <row r="22" spans="1:20" ht="19.2">
       <c r="I22" s="2" t="s">
@@ -13624,6 +13635,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/.trash/易畫165與ASCII94.xlsx
+++ b/.trash/易畫165與ASCII94.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\share\git\rime-jek\.trash\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAB5630-6423-481A-B190-7B704ACC91E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90AEE651-A2CA-480F-9CBD-39BBBFC30110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="9" xr2:uid="{B55F1E0F-6405-49D3-ACBC-C1F7C0B264EC}"/>
   </bookViews>
@@ -9111,13 +9111,13 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{364783B0-24A1-40F6-AA0A-4F4A38EFD675}">
-  <dimension ref="A1:O166"/>
+  <dimension ref="A1:P166"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="12" max="12" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -9134,7 +9134,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:16">
       <c r="A2">
         <v>2630</v>
       </c>
@@ -9179,7 +9179,7 @@
         <v>⚊⚊⚊</v>
       </c>
       <c r="M2" t="str">
-        <f t="shared" ref="M2:O17" si="0">_xlfn.UNICHAR($C2)</f>
+        <f t="shared" ref="M2:P17" si="0">_xlfn.UNICHAR($C2)</f>
         <v>☰</v>
       </c>
       <c r="N2" t="str">
@@ -9187,11 +9187,15 @@
         <v>天</v>
       </c>
       <c r="O2" t="str">
+        <f>M2&amp;N2</f>
+        <v>☰天</v>
+      </c>
+      <c r="P2" t="str">
         <f t="shared" si="0"/>
         <v>☰</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:16">
       <c r="B3" t="str">
         <f t="shared" ref="B3:B66" si="1">DEC2HEX($C3)</f>
         <v>2631</v>
@@ -9241,11 +9245,15 @@
         <v>澤</v>
       </c>
       <c r="O3" t="str">
+        <f t="shared" ref="O3:O66" si="4">M3&amp;N3</f>
+        <v>☱澤</v>
+      </c>
+      <c r="P3" t="str">
         <f t="shared" si="0"/>
         <v>☱</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:16">
       <c r="B4" t="str">
         <f t="shared" si="1"/>
         <v>2632</v>
@@ -9261,7 +9269,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="str">
-        <f t="shared" ref="F4:F166" si="4">_xlfn.UNICHAR($C4)</f>
+        <f t="shared" ref="F4:F166" si="5">_xlfn.UNICHAR($C4)</f>
         <v>☲</v>
       </c>
       <c r="G4" t="s">
@@ -9295,11 +9303,15 @@
         <v>火</v>
       </c>
       <c r="O4" t="str">
+        <f t="shared" si="4"/>
+        <v>☲火</v>
+      </c>
+      <c r="P4" t="str">
         <f t="shared" si="0"/>
         <v>☲</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:16">
       <c r="B5" t="str">
         <f t="shared" si="1"/>
         <v>2633</v>
@@ -9315,7 +9327,7 @@
         <v>4</v>
       </c>
       <c r="F5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>☳</v>
       </c>
       <c r="G5" t="s">
@@ -9349,11 +9361,15 @@
         <v>雷</v>
       </c>
       <c r="O5" t="str">
+        <f t="shared" si="4"/>
+        <v>☳雷</v>
+      </c>
+      <c r="P5" t="str">
         <f t="shared" si="0"/>
         <v>☳</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:16">
       <c r="B6" t="str">
         <f t="shared" si="1"/>
         <v>2634</v>
@@ -9369,7 +9385,7 @@
         <v>5</v>
       </c>
       <c r="F6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>☴</v>
       </c>
       <c r="G6" t="s">
@@ -9403,11 +9419,15 @@
         <v>風</v>
       </c>
       <c r="O6" t="str">
+        <f t="shared" si="4"/>
+        <v>☴風</v>
+      </c>
+      <c r="P6" t="str">
         <f t="shared" si="0"/>
         <v>☴</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:16">
       <c r="B7" t="str">
         <f t="shared" si="1"/>
         <v>2635</v>
@@ -9423,7 +9443,7 @@
         <v>6</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>☵</v>
       </c>
       <c r="G7" t="s">
@@ -9457,11 +9477,15 @@
         <v>水</v>
       </c>
       <c r="O7" t="str">
+        <f t="shared" si="4"/>
+        <v>☵水</v>
+      </c>
+      <c r="P7" t="str">
         <f t="shared" si="0"/>
         <v>☵</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:16">
       <c r="B8" t="str">
         <f t="shared" si="1"/>
         <v>2636</v>
@@ -9477,7 +9501,7 @@
         <v>7</v>
       </c>
       <c r="F8" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>☶</v>
       </c>
       <c r="G8" t="s">
@@ -9511,11 +9535,15 @@
         <v>山</v>
       </c>
       <c r="O8" t="str">
+        <f t="shared" si="4"/>
+        <v>☶山</v>
+      </c>
+      <c r="P8" t="str">
         <f t="shared" si="0"/>
         <v>☶</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:16">
       <c r="B9" t="str">
         <f t="shared" si="1"/>
         <v>2637</v>
@@ -9531,7 +9559,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>☷</v>
       </c>
       <c r="G9" t="s">
@@ -9564,11 +9592,15 @@
         <v>20</v>
       </c>
       <c r="O9" t="str">
+        <f t="shared" si="4"/>
+        <v>☷地</v>
+      </c>
+      <c r="P9" t="str">
         <f t="shared" si="0"/>
         <v>☷</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -9587,7 +9619,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>⚊</v>
       </c>
       <c r="G10" t="s">
@@ -9620,11 +9652,15 @@
         <v>17</v>
       </c>
       <c r="O10" t="str">
+        <f t="shared" si="4"/>
+        <v>⚊陽</v>
+      </c>
+      <c r="P10" t="str">
         <f t="shared" si="0"/>
         <v>⚊</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:16">
       <c r="B11" t="str">
         <f t="shared" si="1"/>
         <v>268B</v>
@@ -9640,7 +9676,7 @@
         <v>2</v>
       </c>
       <c r="F11" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>⚋</v>
       </c>
       <c r="G11" t="s">
@@ -9673,11 +9709,15 @@
         <v>18</v>
       </c>
       <c r="O11" t="str">
+        <f t="shared" si="4"/>
+        <v>⚋陰</v>
+      </c>
+      <c r="P11" t="str">
         <f t="shared" si="0"/>
         <v>⚋</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:16">
       <c r="B12" t="str">
         <f t="shared" si="1"/>
         <v>268C</v>
@@ -9693,7 +9733,7 @@
         <v>1</v>
       </c>
       <c r="F12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>⚌</v>
       </c>
       <c r="G12" t="s">
@@ -9724,11 +9764,15 @@
         <v>老陽</v>
       </c>
       <c r="O12" t="str">
+        <f t="shared" si="4"/>
+        <v>⚌老陽</v>
+      </c>
+      <c r="P12" t="str">
         <f t="shared" si="0"/>
         <v>⚌</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:16">
       <c r="B13" t="str">
         <f t="shared" si="1"/>
         <v>268D</v>
@@ -9744,7 +9788,7 @@
         <v>2</v>
       </c>
       <c r="F13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>⚍</v>
       </c>
       <c r="G13" t="s">
@@ -9775,11 +9819,15 @@
         <v>少陰</v>
       </c>
       <c r="O13" t="str">
+        <f t="shared" si="4"/>
+        <v>⚍少陰</v>
+      </c>
+      <c r="P13" t="str">
         <f t="shared" si="0"/>
         <v>⚍</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:16">
       <c r="B14" t="str">
         <f t="shared" si="1"/>
         <v>268E</v>
@@ -9795,7 +9843,7 @@
         <v>3</v>
       </c>
       <c r="F14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>⚎</v>
       </c>
       <c r="G14" t="s">
@@ -9826,11 +9874,15 @@
         <v>少陽</v>
       </c>
       <c r="O14" t="str">
+        <f t="shared" si="4"/>
+        <v>⚎少陽</v>
+      </c>
+      <c r="P14" t="str">
         <f t="shared" si="0"/>
         <v>⚎</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:16">
       <c r="B15" t="str">
         <f t="shared" si="1"/>
         <v>268F</v>
@@ -9846,7 +9898,7 @@
         <v>4</v>
       </c>
       <c r="F15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>⚏</v>
       </c>
       <c r="G15" t="s">
@@ -9877,11 +9929,15 @@
         <v>老陰</v>
       </c>
       <c r="O15" t="str">
+        <f t="shared" si="4"/>
+        <v>⚏老陰</v>
+      </c>
+      <c r="P15" t="str">
         <f t="shared" si="0"/>
         <v>⚏</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -9900,7 +9956,7 @@
         <v>1</v>
       </c>
       <c r="F16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷀</v>
       </c>
       <c r="G16" t="s">
@@ -9931,11 +9987,15 @@
         <v>乾</v>
       </c>
       <c r="O16" t="str">
+        <f t="shared" si="4"/>
+        <v>䷀乾</v>
+      </c>
+      <c r="P16" t="str">
         <f t="shared" si="0"/>
         <v>䷀</v>
       </c>
     </row>
-    <row r="17" spans="2:15">
+    <row r="17" spans="2:16">
       <c r="B17" t="str">
         <f t="shared" si="1"/>
         <v>4DC1</v>
@@ -9951,7 +10011,7 @@
         <v>2</v>
       </c>
       <c r="F17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷁</v>
       </c>
       <c r="G17" t="s">
@@ -9982,11 +10042,15 @@
         <v>坤</v>
       </c>
       <c r="O17" t="str">
+        <f t="shared" si="4"/>
+        <v>䷁坤</v>
+      </c>
+      <c r="P17" t="str">
         <f t="shared" si="0"/>
         <v>䷁</v>
       </c>
     </row>
-    <row r="18" spans="2:15">
+    <row r="18" spans="2:16">
       <c r="B18" t="str">
         <f t="shared" si="1"/>
         <v>4DC2</v>
@@ -10002,7 +10066,7 @@
         <v>3</v>
       </c>
       <c r="F18" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷂</v>
       </c>
       <c r="G18" t="s">
@@ -10025,7 +10089,7 @@
         <v>⚋⚊⚋⚋⚋⚊</v>
       </c>
       <c r="M18" t="str">
-        <f t="shared" ref="M18:O33" si="5">_xlfn.UNICHAR($C18)</f>
+        <f t="shared" ref="M18:P33" si="6">_xlfn.UNICHAR($C18)</f>
         <v>䷂</v>
       </c>
       <c r="N18" t="str">
@@ -10033,11 +10097,15 @@
         <v>屯</v>
       </c>
       <c r="O18" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
+        <v>䷂屯</v>
+      </c>
+      <c r="P18" t="str">
+        <f t="shared" si="6"/>
         <v>䷂</v>
       </c>
     </row>
-    <row r="19" spans="2:15">
+    <row r="19" spans="2:16">
       <c r="B19" t="str">
         <f t="shared" si="1"/>
         <v>4DC3</v>
@@ -10053,7 +10121,7 @@
         <v>4</v>
       </c>
       <c r="F19" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷃</v>
       </c>
       <c r="G19" t="s">
@@ -10076,7 +10144,7 @@
         <v>⚊⚋⚋⚋⚊⚋</v>
       </c>
       <c r="M19" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>䷃</v>
       </c>
       <c r="N19" t="str">
@@ -10084,11 +10152,15 @@
         <v>蒙</v>
       </c>
       <c r="O19" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
+        <v>䷃蒙</v>
+      </c>
+      <c r="P19" t="str">
+        <f t="shared" si="6"/>
         <v>䷃</v>
       </c>
     </row>
-    <row r="20" spans="2:15">
+    <row r="20" spans="2:16">
       <c r="B20" t="str">
         <f t="shared" si="1"/>
         <v>4DC4</v>
@@ -10104,7 +10176,7 @@
         <v>5</v>
       </c>
       <c r="F20" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷄</v>
       </c>
       <c r="G20" t="s">
@@ -10127,7 +10199,7 @@
         <v>⚋⚊⚋⚊⚊⚊</v>
       </c>
       <c r="M20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>䷄</v>
       </c>
       <c r="N20" t="str">
@@ -10135,11 +10207,15 @@
         <v>需</v>
       </c>
       <c r="O20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
+        <v>䷄需</v>
+      </c>
+      <c r="P20" t="str">
+        <f t="shared" si="6"/>
         <v>䷄</v>
       </c>
     </row>
-    <row r="21" spans="2:15">
+    <row r="21" spans="2:16">
       <c r="B21" t="str">
         <f t="shared" si="1"/>
         <v>4DC5</v>
@@ -10155,7 +10231,7 @@
         <v>6</v>
       </c>
       <c r="F21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷅</v>
       </c>
       <c r="G21" t="s">
@@ -10178,7 +10254,7 @@
         <v>⚊⚊⚊⚋⚊⚋</v>
       </c>
       <c r="M21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>䷅</v>
       </c>
       <c r="N21" t="str">
@@ -10186,11 +10262,15 @@
         <v>訟</v>
       </c>
       <c r="O21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
+        <v>䷅訟</v>
+      </c>
+      <c r="P21" t="str">
+        <f t="shared" si="6"/>
         <v>䷅</v>
       </c>
     </row>
-    <row r="22" spans="2:15">
+    <row r="22" spans="2:16">
       <c r="B22" t="str">
         <f t="shared" si="1"/>
         <v>4DC6</v>
@@ -10206,7 +10286,7 @@
         <v>7</v>
       </c>
       <c r="F22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷆</v>
       </c>
       <c r="G22" t="s">
@@ -10229,7 +10309,7 @@
         <v>⚋⚋⚋⚋⚊⚋</v>
       </c>
       <c r="M22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>䷆</v>
       </c>
       <c r="N22" t="str">
@@ -10237,11 +10317,15 @@
         <v>師</v>
       </c>
       <c r="O22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
+        <v>䷆師</v>
+      </c>
+      <c r="P22" t="str">
+        <f t="shared" si="6"/>
         <v>䷆</v>
       </c>
     </row>
-    <row r="23" spans="2:15">
+    <row r="23" spans="2:16">
       <c r="B23" t="str">
         <f t="shared" si="1"/>
         <v>4DC7</v>
@@ -10257,7 +10341,7 @@
         <v>8</v>
       </c>
       <c r="F23" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷇</v>
       </c>
       <c r="G23" t="s">
@@ -10280,7 +10364,7 @@
         <v>⚋⚊⚋⚋⚋⚋</v>
       </c>
       <c r="M23" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>䷇</v>
       </c>
       <c r="N23" t="str">
@@ -10288,11 +10372,15 @@
         <v>比</v>
       </c>
       <c r="O23" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
+        <v>䷇比</v>
+      </c>
+      <c r="P23" t="str">
+        <f t="shared" si="6"/>
         <v>䷇</v>
       </c>
     </row>
-    <row r="24" spans="2:15">
+    <row r="24" spans="2:16">
       <c r="B24" t="str">
         <f t="shared" si="1"/>
         <v>4DC8</v>
@@ -10308,7 +10396,7 @@
         <v>9</v>
       </c>
       <c r="F24" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷈</v>
       </c>
       <c r="G24" t="s">
@@ -10331,7 +10419,7 @@
         <v>⚊⚊⚋⚊⚊⚊</v>
       </c>
       <c r="M24" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>䷈</v>
       </c>
       <c r="N24" t="str">
@@ -10339,11 +10427,15 @@
         <v>小畜</v>
       </c>
       <c r="O24" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
+        <v>䷈小畜</v>
+      </c>
+      <c r="P24" t="str">
+        <f t="shared" si="6"/>
         <v>䷈</v>
       </c>
     </row>
-    <row r="25" spans="2:15">
+    <row r="25" spans="2:16">
       <c r="B25" t="str">
         <f t="shared" si="1"/>
         <v>4DC9</v>
@@ -10359,7 +10451,7 @@
         <v>10</v>
       </c>
       <c r="F25" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷉</v>
       </c>
       <c r="G25" t="s">
@@ -10382,7 +10474,7 @@
         <v>⚊⚊⚊⚋⚊⚊</v>
       </c>
       <c r="M25" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>䷉</v>
       </c>
       <c r="N25" t="str">
@@ -10390,11 +10482,15 @@
         <v>履</v>
       </c>
       <c r="O25" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
+        <v>䷉履</v>
+      </c>
+      <c r="P25" t="str">
+        <f t="shared" si="6"/>
         <v>䷉</v>
       </c>
     </row>
-    <row r="26" spans="2:15">
+    <row r="26" spans="2:16">
       <c r="B26" t="str">
         <f t="shared" si="1"/>
         <v>4DCA</v>
@@ -10410,7 +10506,7 @@
         <v>11</v>
       </c>
       <c r="F26" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷊</v>
       </c>
       <c r="G26" t="s">
@@ -10433,7 +10529,7 @@
         <v>⚋⚋⚋⚊⚊⚊</v>
       </c>
       <c r="M26" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>䷊</v>
       </c>
       <c r="N26" t="str">
@@ -10441,11 +10537,15 @@
         <v>泰</v>
       </c>
       <c r="O26" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
+        <v>䷊泰</v>
+      </c>
+      <c r="P26" t="str">
+        <f t="shared" si="6"/>
         <v>䷊</v>
       </c>
     </row>
-    <row r="27" spans="2:15">
+    <row r="27" spans="2:16">
       <c r="B27" t="str">
         <f t="shared" si="1"/>
         <v>4DCB</v>
@@ -10461,7 +10561,7 @@
         <v>12</v>
       </c>
       <c r="F27" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷋</v>
       </c>
       <c r="G27" t="s">
@@ -10484,7 +10584,7 @@
         <v>⚊⚊⚊⚋⚋⚋</v>
       </c>
       <c r="M27" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>䷋</v>
       </c>
       <c r="N27" t="str">
@@ -10492,11 +10592,15 @@
         <v>否</v>
       </c>
       <c r="O27" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
+        <v>䷋否</v>
+      </c>
+      <c r="P27" t="str">
+        <f t="shared" si="6"/>
         <v>䷋</v>
       </c>
     </row>
-    <row r="28" spans="2:15">
+    <row r="28" spans="2:16">
       <c r="B28" t="str">
         <f t="shared" si="1"/>
         <v>4DCC</v>
@@ -10512,7 +10616,7 @@
         <v>13</v>
       </c>
       <c r="F28" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷌</v>
       </c>
       <c r="G28" t="s">
@@ -10535,7 +10639,7 @@
         <v>⚊⚊⚊⚊⚋⚊</v>
       </c>
       <c r="M28" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>䷌</v>
       </c>
       <c r="N28" t="str">
@@ -10543,11 +10647,15 @@
         <v>同人</v>
       </c>
       <c r="O28" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
+        <v>䷌同人</v>
+      </c>
+      <c r="P28" t="str">
+        <f t="shared" si="6"/>
         <v>䷌</v>
       </c>
     </row>
-    <row r="29" spans="2:15">
+    <row r="29" spans="2:16">
       <c r="B29" t="str">
         <f t="shared" si="1"/>
         <v>4DCD</v>
@@ -10563,7 +10671,7 @@
         <v>14</v>
       </c>
       <c r="F29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷍</v>
       </c>
       <c r="G29" t="s">
@@ -10586,7 +10694,7 @@
         <v>⚊⚋⚊⚊⚊⚊</v>
       </c>
       <c r="M29" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>䷍</v>
       </c>
       <c r="N29" t="str">
@@ -10594,11 +10702,15 @@
         <v>大有</v>
       </c>
       <c r="O29" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
+        <v>䷍大有</v>
+      </c>
+      <c r="P29" t="str">
+        <f t="shared" si="6"/>
         <v>䷍</v>
       </c>
     </row>
-    <row r="30" spans="2:15">
+    <row r="30" spans="2:16">
       <c r="B30" t="str">
         <f t="shared" si="1"/>
         <v>4DCE</v>
@@ -10614,7 +10726,7 @@
         <v>15</v>
       </c>
       <c r="F30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷎</v>
       </c>
       <c r="G30" t="s">
@@ -10637,7 +10749,7 @@
         <v>⚋⚋⚋⚊⚋⚋</v>
       </c>
       <c r="M30" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>䷎</v>
       </c>
       <c r="N30" t="str">
@@ -10645,11 +10757,15 @@
         <v>謙</v>
       </c>
       <c r="O30" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
+        <v>䷎謙</v>
+      </c>
+      <c r="P30" t="str">
+        <f t="shared" si="6"/>
         <v>䷎</v>
       </c>
     </row>
-    <row r="31" spans="2:15">
+    <row r="31" spans="2:16">
       <c r="B31" t="str">
         <f t="shared" si="1"/>
         <v>4DCF</v>
@@ -10665,7 +10781,7 @@
         <v>16</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷏</v>
       </c>
       <c r="G31" t="s">
@@ -10688,7 +10804,7 @@
         <v>⚋⚋⚊⚋⚋⚋</v>
       </c>
       <c r="M31" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>䷏</v>
       </c>
       <c r="N31" t="str">
@@ -10696,11 +10812,15 @@
         <v>豫</v>
       </c>
       <c r="O31" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
+        <v>䷏豫</v>
+      </c>
+      <c r="P31" t="str">
+        <f t="shared" si="6"/>
         <v>䷏</v>
       </c>
     </row>
-    <row r="32" spans="2:15">
+    <row r="32" spans="2:16">
       <c r="B32" t="str">
         <f t="shared" si="1"/>
         <v>4DD0</v>
@@ -10716,7 +10836,7 @@
         <v>17</v>
       </c>
       <c r="F32" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷐</v>
       </c>
       <c r="G32" t="s">
@@ -10739,7 +10859,7 @@
         <v>⚋⚊⚊⚋⚋⚊</v>
       </c>
       <c r="M32" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>䷐</v>
       </c>
       <c r="N32" t="str">
@@ -10747,11 +10867,15 @@
         <v>隨</v>
       </c>
       <c r="O32" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
+        <v>䷐隨</v>
+      </c>
+      <c r="P32" t="str">
+        <f t="shared" si="6"/>
         <v>䷐</v>
       </c>
     </row>
-    <row r="33" spans="2:15">
+    <row r="33" spans="2:16">
       <c r="B33" t="str">
         <f t="shared" si="1"/>
         <v>4DD1</v>
@@ -10767,7 +10891,7 @@
         <v>18</v>
       </c>
       <c r="F33" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷑</v>
       </c>
       <c r="G33" t="s">
@@ -10790,7 +10914,7 @@
         <v>⚊⚋⚋⚊⚊⚋</v>
       </c>
       <c r="M33" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>䷑</v>
       </c>
       <c r="N33" t="str">
@@ -10798,11 +10922,15 @@
         <v>蠱</v>
       </c>
       <c r="O33" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
+        <v>䷑蠱</v>
+      </c>
+      <c r="P33" t="str">
+        <f t="shared" si="6"/>
         <v>䷑</v>
       </c>
     </row>
-    <row r="34" spans="2:15">
+    <row r="34" spans="2:16">
       <c r="B34" t="str">
         <f t="shared" si="1"/>
         <v>4DD2</v>
@@ -10818,7 +10946,7 @@
         <v>19</v>
       </c>
       <c r="F34" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷒</v>
       </c>
       <c r="G34" t="s">
@@ -10841,7 +10969,7 @@
         <v>⚋⚋⚋⚋⚊⚊</v>
       </c>
       <c r="M34" t="str">
-        <f t="shared" ref="M34:O49" si="6">_xlfn.UNICHAR($C34)</f>
+        <f t="shared" ref="M34:P49" si="7">_xlfn.UNICHAR($C34)</f>
         <v>䷒</v>
       </c>
       <c r="N34" t="str">
@@ -10849,11 +10977,15 @@
         <v>臨</v>
       </c>
       <c r="O34" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
+        <v>䷒臨</v>
+      </c>
+      <c r="P34" t="str">
+        <f t="shared" si="7"/>
         <v>䷒</v>
       </c>
     </row>
-    <row r="35" spans="2:15">
+    <row r="35" spans="2:16">
       <c r="B35" t="str">
         <f t="shared" si="1"/>
         <v>4DD3</v>
@@ -10869,7 +11001,7 @@
         <v>20</v>
       </c>
       <c r="F35" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷓</v>
       </c>
       <c r="G35" t="s">
@@ -10892,7 +11024,7 @@
         <v>⚊⚊⚋⚋⚋⚋</v>
       </c>
       <c r="M35" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>䷓</v>
       </c>
       <c r="N35" t="str">
@@ -10900,11 +11032,15 @@
         <v>觀</v>
       </c>
       <c r="O35" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
+        <v>䷓觀</v>
+      </c>
+      <c r="P35" t="str">
+        <f t="shared" si="7"/>
         <v>䷓</v>
       </c>
     </row>
-    <row r="36" spans="2:15">
+    <row r="36" spans="2:16">
       <c r="B36" t="str">
         <f t="shared" si="1"/>
         <v>4DD4</v>
@@ -10920,7 +11056,7 @@
         <v>21</v>
       </c>
       <c r="F36" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷔</v>
       </c>
       <c r="G36" t="s">
@@ -10943,7 +11079,7 @@
         <v>⚊⚋⚊⚋⚋⚊</v>
       </c>
       <c r="M36" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>䷔</v>
       </c>
       <c r="N36" t="str">
@@ -10951,11 +11087,15 @@
         <v>噬嗑</v>
       </c>
       <c r="O36" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
+        <v>䷔噬嗑</v>
+      </c>
+      <c r="P36" t="str">
+        <f t="shared" si="7"/>
         <v>䷔</v>
       </c>
     </row>
-    <row r="37" spans="2:15">
+    <row r="37" spans="2:16">
       <c r="B37" t="str">
         <f t="shared" si="1"/>
         <v>4DD5</v>
@@ -10971,7 +11111,7 @@
         <v>22</v>
       </c>
       <c r="F37" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷕</v>
       </c>
       <c r="G37" t="s">
@@ -10994,7 +11134,7 @@
         <v>⚊⚋⚋⚊⚋⚊</v>
       </c>
       <c r="M37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>䷕</v>
       </c>
       <c r="N37" t="str">
@@ -11002,11 +11142,15 @@
         <v>賁</v>
       </c>
       <c r="O37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
+        <v>䷕賁</v>
+      </c>
+      <c r="P37" t="str">
+        <f t="shared" si="7"/>
         <v>䷕</v>
       </c>
     </row>
-    <row r="38" spans="2:15">
+    <row r="38" spans="2:16">
       <c r="B38" t="str">
         <f t="shared" si="1"/>
         <v>4DD6</v>
@@ -11022,7 +11166,7 @@
         <v>23</v>
       </c>
       <c r="F38" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷖</v>
       </c>
       <c r="G38" t="s">
@@ -11045,7 +11189,7 @@
         <v>⚊⚋⚋⚋⚋⚋</v>
       </c>
       <c r="M38" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>䷖</v>
       </c>
       <c r="N38" t="str">
@@ -11053,11 +11197,15 @@
         <v>剝</v>
       </c>
       <c r="O38" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
+        <v>䷖剝</v>
+      </c>
+      <c r="P38" t="str">
+        <f t="shared" si="7"/>
         <v>䷖</v>
       </c>
     </row>
-    <row r="39" spans="2:15">
+    <row r="39" spans="2:16">
       <c r="B39" t="str">
         <f t="shared" si="1"/>
         <v>4DD7</v>
@@ -11073,7 +11221,7 @@
         <v>24</v>
       </c>
       <c r="F39" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷗</v>
       </c>
       <c r="G39" t="s">
@@ -11096,7 +11244,7 @@
         <v>⚋⚋⚋⚋⚋⚊</v>
       </c>
       <c r="M39" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>䷗</v>
       </c>
       <c r="N39" t="str">
@@ -11104,11 +11252,15 @@
         <v>復</v>
       </c>
       <c r="O39" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
+        <v>䷗復</v>
+      </c>
+      <c r="P39" t="str">
+        <f t="shared" si="7"/>
         <v>䷗</v>
       </c>
     </row>
-    <row r="40" spans="2:15">
+    <row r="40" spans="2:16">
       <c r="B40" t="str">
         <f t="shared" si="1"/>
         <v>4DD8</v>
@@ -11124,7 +11276,7 @@
         <v>25</v>
       </c>
       <c r="F40" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷘</v>
       </c>
       <c r="G40" t="s">
@@ -11147,7 +11299,7 @@
         <v>⚊⚊⚊⚋⚋⚊</v>
       </c>
       <c r="M40" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>䷘</v>
       </c>
       <c r="N40" t="str">
@@ -11155,11 +11307,15 @@
         <v>无妄</v>
       </c>
       <c r="O40" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
+        <v>䷘无妄</v>
+      </c>
+      <c r="P40" t="str">
+        <f t="shared" si="7"/>
         <v>䷘</v>
       </c>
     </row>
-    <row r="41" spans="2:15">
+    <row r="41" spans="2:16">
       <c r="B41" t="str">
         <f t="shared" si="1"/>
         <v>4DD9</v>
@@ -11175,7 +11331,7 @@
         <v>26</v>
       </c>
       <c r="F41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷙</v>
       </c>
       <c r="G41" t="s">
@@ -11198,7 +11354,7 @@
         <v>⚊⚋⚋⚊⚊⚊</v>
       </c>
       <c r="M41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>䷙</v>
       </c>
       <c r="N41" t="str">
@@ -11206,11 +11362,15 @@
         <v>大畜</v>
       </c>
       <c r="O41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
+        <v>䷙大畜</v>
+      </c>
+      <c r="P41" t="str">
+        <f t="shared" si="7"/>
         <v>䷙</v>
       </c>
     </row>
-    <row r="42" spans="2:15">
+    <row r="42" spans="2:16">
       <c r="B42" t="str">
         <f t="shared" si="1"/>
         <v>4DDA</v>
@@ -11226,7 +11386,7 @@
         <v>27</v>
       </c>
       <c r="F42" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷚</v>
       </c>
       <c r="G42" t="s">
@@ -11249,7 +11409,7 @@
         <v>⚊⚋⚋⚋⚋⚊</v>
       </c>
       <c r="M42" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>䷚</v>
       </c>
       <c r="N42" t="str">
@@ -11257,11 +11417,15 @@
         <v>頤</v>
       </c>
       <c r="O42" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
+        <v>䷚頤</v>
+      </c>
+      <c r="P42" t="str">
+        <f t="shared" si="7"/>
         <v>䷚</v>
       </c>
     </row>
-    <row r="43" spans="2:15">
+    <row r="43" spans="2:16">
       <c r="B43" t="str">
         <f t="shared" si="1"/>
         <v>4DDB</v>
@@ -11277,7 +11441,7 @@
         <v>28</v>
       </c>
       <c r="F43" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷛</v>
       </c>
       <c r="G43" t="s">
@@ -11300,7 +11464,7 @@
         <v>⚋⚊⚊⚊⚊⚋</v>
       </c>
       <c r="M43" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>䷛</v>
       </c>
       <c r="N43" t="str">
@@ -11308,11 +11472,15 @@
         <v>大過</v>
       </c>
       <c r="O43" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
+        <v>䷛大過</v>
+      </c>
+      <c r="P43" t="str">
+        <f t="shared" si="7"/>
         <v>䷛</v>
       </c>
     </row>
-    <row r="44" spans="2:15">
+    <row r="44" spans="2:16">
       <c r="B44" t="str">
         <f t="shared" si="1"/>
         <v>4DDC</v>
@@ -11328,7 +11496,7 @@
         <v>29</v>
       </c>
       <c r="F44" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷜</v>
       </c>
       <c r="G44" t="s">
@@ -11351,7 +11519,7 @@
         <v>⚋⚊⚋⚋⚊⚋</v>
       </c>
       <c r="M44" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>䷜</v>
       </c>
       <c r="N44" t="str">
@@ -11359,11 +11527,15 @@
         <v>坎</v>
       </c>
       <c r="O44" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
+        <v>䷜坎</v>
+      </c>
+      <c r="P44" t="str">
+        <f t="shared" si="7"/>
         <v>䷜</v>
       </c>
     </row>
-    <row r="45" spans="2:15">
+    <row r="45" spans="2:16">
       <c r="B45" t="str">
         <f t="shared" si="1"/>
         <v>4DDD</v>
@@ -11379,7 +11551,7 @@
         <v>30</v>
       </c>
       <c r="F45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷝</v>
       </c>
       <c r="G45" t="s">
@@ -11402,7 +11574,7 @@
         <v>⚊⚋⚊⚊⚋⚊</v>
       </c>
       <c r="M45" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>䷝</v>
       </c>
       <c r="N45" t="str">
@@ -11410,11 +11582,15 @@
         <v>離</v>
       </c>
       <c r="O45" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
+        <v>䷝離</v>
+      </c>
+      <c r="P45" t="str">
+        <f t="shared" si="7"/>
         <v>䷝</v>
       </c>
     </row>
-    <row r="46" spans="2:15">
+    <row r="46" spans="2:16">
       <c r="B46" t="str">
         <f t="shared" si="1"/>
         <v>4DDE</v>
@@ -11430,7 +11606,7 @@
         <v>31</v>
       </c>
       <c r="F46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷞</v>
       </c>
       <c r="G46" t="s">
@@ -11453,7 +11629,7 @@
         <v>⚋⚊⚊⚊⚋⚋</v>
       </c>
       <c r="M46" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>䷞</v>
       </c>
       <c r="N46" t="str">
@@ -11461,11 +11637,15 @@
         <v>咸</v>
       </c>
       <c r="O46" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
+        <v>䷞咸</v>
+      </c>
+      <c r="P46" t="str">
+        <f t="shared" si="7"/>
         <v>䷞</v>
       </c>
     </row>
-    <row r="47" spans="2:15">
+    <row r="47" spans="2:16">
       <c r="B47" t="str">
         <f t="shared" si="1"/>
         <v>4DDF</v>
@@ -11481,7 +11661,7 @@
         <v>32</v>
       </c>
       <c r="F47" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷟</v>
       </c>
       <c r="G47" t="s">
@@ -11504,7 +11684,7 @@
         <v>⚋⚋⚊⚊⚊⚋</v>
       </c>
       <c r="M47" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>䷟</v>
       </c>
       <c r="N47" t="str">
@@ -11512,11 +11692,15 @@
         <v>恆</v>
       </c>
       <c r="O47" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
+        <v>䷟恆</v>
+      </c>
+      <c r="P47" t="str">
+        <f t="shared" si="7"/>
         <v>䷟</v>
       </c>
     </row>
-    <row r="48" spans="2:15">
+    <row r="48" spans="2:16">
       <c r="B48" t="str">
         <f t="shared" si="1"/>
         <v>4DE0</v>
@@ -11532,7 +11716,7 @@
         <v>33</v>
       </c>
       <c r="F48" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷠</v>
       </c>
       <c r="G48" t="s">
@@ -11555,7 +11739,7 @@
         <v>⚊⚊⚊⚊⚋⚋</v>
       </c>
       <c r="M48" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>䷠</v>
       </c>
       <c r="N48" t="str">
@@ -11563,11 +11747,15 @@
         <v>遯</v>
       </c>
       <c r="O48" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
+        <v>䷠遯</v>
+      </c>
+      <c r="P48" t="str">
+        <f t="shared" si="7"/>
         <v>䷠</v>
       </c>
     </row>
-    <row r="49" spans="2:15">
+    <row r="49" spans="2:16">
       <c r="B49" t="str">
         <f t="shared" si="1"/>
         <v>4DE1</v>
@@ -11583,7 +11771,7 @@
         <v>34</v>
       </c>
       <c r="F49" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷡</v>
       </c>
       <c r="G49" t="s">
@@ -11606,7 +11794,7 @@
         <v>⚋⚋⚊⚊⚊⚊</v>
       </c>
       <c r="M49" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>䷡</v>
       </c>
       <c r="N49" t="str">
@@ -11614,11 +11802,15 @@
         <v>大壯</v>
       </c>
       <c r="O49" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
+        <v>䷡大壯</v>
+      </c>
+      <c r="P49" t="str">
+        <f t="shared" si="7"/>
         <v>䷡</v>
       </c>
     </row>
-    <row r="50" spans="2:15">
+    <row r="50" spans="2:16">
       <c r="B50" t="str">
         <f t="shared" si="1"/>
         <v>4DE2</v>
@@ -11634,7 +11826,7 @@
         <v>35</v>
       </c>
       <c r="F50" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷢</v>
       </c>
       <c r="G50" t="s">
@@ -11657,7 +11849,7 @@
         <v>⚊⚋⚊⚋⚋⚋</v>
       </c>
       <c r="M50" t="str">
-        <f t="shared" ref="M50:O65" si="7">_xlfn.UNICHAR($C50)</f>
+        <f t="shared" ref="M50:P65" si="8">_xlfn.UNICHAR($C50)</f>
         <v>䷢</v>
       </c>
       <c r="N50" t="str">
@@ -11665,11 +11857,15 @@
         <v>晉</v>
       </c>
       <c r="O50" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
+        <v>䷢晉</v>
+      </c>
+      <c r="P50" t="str">
+        <f t="shared" si="8"/>
         <v>䷢</v>
       </c>
     </row>
-    <row r="51" spans="2:15">
+    <row r="51" spans="2:16">
       <c r="B51" t="str">
         <f t="shared" si="1"/>
         <v>4DE3</v>
@@ -11685,7 +11881,7 @@
         <v>36</v>
       </c>
       <c r="F51" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷣</v>
       </c>
       <c r="G51" t="s">
@@ -11708,7 +11904,7 @@
         <v>⚋⚋⚋⚊⚋⚊</v>
       </c>
       <c r="M51" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>䷣</v>
       </c>
       <c r="N51" t="str">
@@ -11716,11 +11912,15 @@
         <v>明夷</v>
       </c>
       <c r="O51" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
+        <v>䷣明夷</v>
+      </c>
+      <c r="P51" t="str">
+        <f t="shared" si="8"/>
         <v>䷣</v>
       </c>
     </row>
-    <row r="52" spans="2:15">
+    <row r="52" spans="2:16">
       <c r="B52" t="str">
         <f t="shared" si="1"/>
         <v>4DE4</v>
@@ -11736,7 +11936,7 @@
         <v>37</v>
       </c>
       <c r="F52" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷤</v>
       </c>
       <c r="G52" t="s">
@@ -11759,7 +11959,7 @@
         <v>⚊⚊⚋⚊⚋⚊</v>
       </c>
       <c r="M52" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>䷤</v>
       </c>
       <c r="N52" t="str">
@@ -11767,11 +11967,15 @@
         <v>家人</v>
       </c>
       <c r="O52" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
+        <v>䷤家人</v>
+      </c>
+      <c r="P52" t="str">
+        <f t="shared" si="8"/>
         <v>䷤</v>
       </c>
     </row>
-    <row r="53" spans="2:15">
+    <row r="53" spans="2:16">
       <c r="B53" t="str">
         <f t="shared" si="1"/>
         <v>4DE5</v>
@@ -11787,7 +11991,7 @@
         <v>38</v>
       </c>
       <c r="F53" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷥</v>
       </c>
       <c r="G53" t="s">
@@ -11810,7 +12014,7 @@
         <v>⚊⚋⚊⚋⚊⚊</v>
       </c>
       <c r="M53" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>䷥</v>
       </c>
       <c r="N53" t="str">
@@ -11818,11 +12022,15 @@
         <v>睽</v>
       </c>
       <c r="O53" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
+        <v>䷥睽</v>
+      </c>
+      <c r="P53" t="str">
+        <f t="shared" si="8"/>
         <v>䷥</v>
       </c>
     </row>
-    <row r="54" spans="2:15">
+    <row r="54" spans="2:16">
       <c r="B54" t="str">
         <f t="shared" si="1"/>
         <v>4DE6</v>
@@ -11838,7 +12046,7 @@
         <v>39</v>
       </c>
       <c r="F54" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷦</v>
       </c>
       <c r="G54" t="s">
@@ -11861,7 +12069,7 @@
         <v>⚋⚊⚋⚊⚋⚋</v>
       </c>
       <c r="M54" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>䷦</v>
       </c>
       <c r="N54" t="str">
@@ -11869,11 +12077,15 @@
         <v>蹇</v>
       </c>
       <c r="O54" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
+        <v>䷦蹇</v>
+      </c>
+      <c r="P54" t="str">
+        <f t="shared" si="8"/>
         <v>䷦</v>
       </c>
     </row>
-    <row r="55" spans="2:15">
+    <row r="55" spans="2:16">
       <c r="B55" t="str">
         <f t="shared" si="1"/>
         <v>4DE7</v>
@@ -11889,7 +12101,7 @@
         <v>40</v>
       </c>
       <c r="F55" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷧</v>
       </c>
       <c r="G55" t="s">
@@ -11912,7 +12124,7 @@
         <v>⚋⚋⚊⚋⚊⚋</v>
       </c>
       <c r="M55" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>䷧</v>
       </c>
       <c r="N55" t="str">
@@ -11920,11 +12132,15 @@
         <v>解</v>
       </c>
       <c r="O55" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
+        <v>䷧解</v>
+      </c>
+      <c r="P55" t="str">
+        <f t="shared" si="8"/>
         <v>䷧</v>
       </c>
     </row>
-    <row r="56" spans="2:15">
+    <row r="56" spans="2:16">
       <c r="B56" t="str">
         <f t="shared" si="1"/>
         <v>4DE8</v>
@@ -11940,7 +12156,7 @@
         <v>41</v>
       </c>
       <c r="F56" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷨</v>
       </c>
       <c r="G56" t="s">
@@ -11963,7 +12179,7 @@
         <v>⚊⚋⚋⚋⚊⚊</v>
       </c>
       <c r="M56" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>䷨</v>
       </c>
       <c r="N56" t="str">
@@ -11971,11 +12187,15 @@
         <v>損</v>
       </c>
       <c r="O56" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
+        <v>䷨損</v>
+      </c>
+      <c r="P56" t="str">
+        <f t="shared" si="8"/>
         <v>䷨</v>
       </c>
     </row>
-    <row r="57" spans="2:15">
+    <row r="57" spans="2:16">
       <c r="B57" t="str">
         <f t="shared" si="1"/>
         <v>4DE9</v>
@@ -11991,7 +12211,7 @@
         <v>42</v>
       </c>
       <c r="F57" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷩</v>
       </c>
       <c r="G57" t="s">
@@ -12014,7 +12234,7 @@
         <v>⚊⚊⚋⚋⚋⚊</v>
       </c>
       <c r="M57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>䷩</v>
       </c>
       <c r="N57" t="str">
@@ -12022,11 +12242,15 @@
         <v>益</v>
       </c>
       <c r="O57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
+        <v>䷩益</v>
+      </c>
+      <c r="P57" t="str">
+        <f t="shared" si="8"/>
         <v>䷩</v>
       </c>
     </row>
-    <row r="58" spans="2:15">
+    <row r="58" spans="2:16">
       <c r="B58" t="str">
         <f t="shared" si="1"/>
         <v>4DEA</v>
@@ -12042,7 +12266,7 @@
         <v>43</v>
       </c>
       <c r="F58" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷪</v>
       </c>
       <c r="G58" t="s">
@@ -12065,7 +12289,7 @@
         <v>⚋⚊⚊⚊⚊⚊</v>
       </c>
       <c r="M58" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>䷪</v>
       </c>
       <c r="N58" t="str">
@@ -12073,11 +12297,15 @@
         <v>夬</v>
       </c>
       <c r="O58" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
+        <v>䷪夬</v>
+      </c>
+      <c r="P58" t="str">
+        <f t="shared" si="8"/>
         <v>䷪</v>
       </c>
     </row>
-    <row r="59" spans="2:15">
+    <row r="59" spans="2:16">
       <c r="B59" t="str">
         <f t="shared" si="1"/>
         <v>4DEB</v>
@@ -12093,7 +12321,7 @@
         <v>44</v>
       </c>
       <c r="F59" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷫</v>
       </c>
       <c r="G59" t="s">
@@ -12116,7 +12344,7 @@
         <v>⚊⚊⚊⚊⚊⚋</v>
       </c>
       <c r="M59" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>䷫</v>
       </c>
       <c r="N59" t="str">
@@ -12124,11 +12352,15 @@
         <v>姤</v>
       </c>
       <c r="O59" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
+        <v>䷫姤</v>
+      </c>
+      <c r="P59" t="str">
+        <f t="shared" si="8"/>
         <v>䷫</v>
       </c>
     </row>
-    <row r="60" spans="2:15">
+    <row r="60" spans="2:16">
       <c r="B60" t="str">
         <f t="shared" si="1"/>
         <v>4DEC</v>
@@ -12144,7 +12376,7 @@
         <v>45</v>
       </c>
       <c r="F60" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷬</v>
       </c>
       <c r="G60" t="s">
@@ -12167,7 +12399,7 @@
         <v>⚋⚊⚊⚋⚋⚋</v>
       </c>
       <c r="M60" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>䷬</v>
       </c>
       <c r="N60" t="str">
@@ -12175,11 +12407,15 @@
         <v>萃</v>
       </c>
       <c r="O60" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
+        <v>䷬萃</v>
+      </c>
+      <c r="P60" t="str">
+        <f t="shared" si="8"/>
         <v>䷬</v>
       </c>
     </row>
-    <row r="61" spans="2:15">
+    <row r="61" spans="2:16">
       <c r="B61" t="str">
         <f t="shared" si="1"/>
         <v>4DED</v>
@@ -12195,7 +12431,7 @@
         <v>46</v>
       </c>
       <c r="F61" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷭</v>
       </c>
       <c r="G61" t="s">
@@ -12218,7 +12454,7 @@
         <v>⚋⚋⚋⚊⚊⚋</v>
       </c>
       <c r="M61" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>䷭</v>
       </c>
       <c r="N61" t="str">
@@ -12226,11 +12462,15 @@
         <v>升</v>
       </c>
       <c r="O61" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
+        <v>䷭升</v>
+      </c>
+      <c r="P61" t="str">
+        <f t="shared" si="8"/>
         <v>䷭</v>
       </c>
     </row>
-    <row r="62" spans="2:15">
+    <row r="62" spans="2:16">
       <c r="B62" t="str">
         <f t="shared" si="1"/>
         <v>4DEE</v>
@@ -12246,7 +12486,7 @@
         <v>47</v>
       </c>
       <c r="F62" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷮</v>
       </c>
       <c r="G62" t="s">
@@ -12269,7 +12509,7 @@
         <v>⚋⚊⚊⚋⚊⚋</v>
       </c>
       <c r="M62" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>䷮</v>
       </c>
       <c r="N62" t="str">
@@ -12277,11 +12517,15 @@
         <v>困</v>
       </c>
       <c r="O62" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
+        <v>䷮困</v>
+      </c>
+      <c r="P62" t="str">
+        <f t="shared" si="8"/>
         <v>䷮</v>
       </c>
     </row>
-    <row r="63" spans="2:15">
+    <row r="63" spans="2:16">
       <c r="B63" t="str">
         <f t="shared" si="1"/>
         <v>4DEF</v>
@@ -12297,7 +12541,7 @@
         <v>48</v>
       </c>
       <c r="F63" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷯</v>
       </c>
       <c r="G63" t="s">
@@ -12320,7 +12564,7 @@
         <v>⚋⚊⚋⚊⚊⚋</v>
       </c>
       <c r="M63" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>䷯</v>
       </c>
       <c r="N63" t="str">
@@ -12328,11 +12572,15 @@
         <v>井</v>
       </c>
       <c r="O63" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
+        <v>䷯井</v>
+      </c>
+      <c r="P63" t="str">
+        <f t="shared" si="8"/>
         <v>䷯</v>
       </c>
     </row>
-    <row r="64" spans="2:15">
+    <row r="64" spans="2:16">
       <c r="B64" t="str">
         <f t="shared" si="1"/>
         <v>4DF0</v>
@@ -12348,7 +12596,7 @@
         <v>49</v>
       </c>
       <c r="F64" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷰</v>
       </c>
       <c r="G64" t="s">
@@ -12371,7 +12619,7 @@
         <v>⚋⚊⚊⚊⚋⚊</v>
       </c>
       <c r="M64" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>䷰</v>
       </c>
       <c r="N64" t="str">
@@ -12379,11 +12627,15 @@
         <v>革</v>
       </c>
       <c r="O64" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
+        <v>䷰革</v>
+      </c>
+      <c r="P64" t="str">
+        <f t="shared" si="8"/>
         <v>䷰</v>
       </c>
     </row>
-    <row r="65" spans="1:15">
+    <row r="65" spans="1:16">
       <c r="B65" t="str">
         <f t="shared" si="1"/>
         <v>4DF1</v>
@@ -12399,7 +12651,7 @@
         <v>50</v>
       </c>
       <c r="F65" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷱</v>
       </c>
       <c r="G65" t="s">
@@ -12422,7 +12674,7 @@
         <v>⚊⚋⚊⚊⚊⚋</v>
       </c>
       <c r="M65" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>䷱</v>
       </c>
       <c r="N65" t="str">
@@ -12430,11 +12682,15 @@
         <v>鼎</v>
       </c>
       <c r="O65" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
+        <v>䷱鼎</v>
+      </c>
+      <c r="P65" t="str">
+        <f t="shared" si="8"/>
         <v>䷱</v>
       </c>
     </row>
-    <row r="66" spans="1:15">
+    <row r="66" spans="1:16">
       <c r="B66" t="str">
         <f t="shared" si="1"/>
         <v>4DF2</v>
@@ -12450,7 +12706,7 @@
         <v>51</v>
       </c>
       <c r="F66" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷲</v>
       </c>
       <c r="G66" t="s">
@@ -12473,7 +12729,7 @@
         <v>⚋⚋⚊⚋⚋⚊</v>
       </c>
       <c r="M66" t="str">
-        <f t="shared" ref="M66:O81" si="8">_xlfn.UNICHAR($C66)</f>
+        <f t="shared" ref="M66:P81" si="9">_xlfn.UNICHAR($C66)</f>
         <v>䷲</v>
       </c>
       <c r="N66" t="str">
@@ -12481,13 +12737,17 @@
         <v>震</v>
       </c>
       <c r="O66" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
+        <v>䷲震</v>
+      </c>
+      <c r="P66" t="str">
+        <f t="shared" si="9"/>
         <v>䷲</v>
       </c>
     </row>
-    <row r="67" spans="1:15">
+    <row r="67" spans="1:16">
       <c r="B67" t="str">
-        <f t="shared" ref="B67:B130" si="9">DEC2HEX($C67)</f>
+        <f t="shared" ref="B67:B130" si="10">DEC2HEX($C67)</f>
         <v>4DF3</v>
       </c>
       <c r="C67" cm="1">
@@ -12501,7 +12761,7 @@
         <v>52</v>
       </c>
       <c r="F67" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷳</v>
       </c>
       <c r="G67" t="s">
@@ -12520,25 +12780,29 @@
         <v>788788</v>
       </c>
       <c r="L67" t="str">
-        <f t="shared" ref="L67:L85" si="10">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TEXT($J67,"0"),"1","⚊"),"2","⚋"),"3","𝌀")</f>
+        <f t="shared" ref="L67:L85" si="11">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TEXT($J67,"0"),"1","⚊"),"2","⚋"),"3","𝌀")</f>
         <v>⚊⚋⚋⚊⚋⚋</v>
       </c>
       <c r="M67" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>䷳</v>
       </c>
       <c r="N67" t="str">
-        <f t="shared" ref="N67:N130" si="11">IF($H67="",$G67,$H67)</f>
+        <f t="shared" ref="N67:N130" si="12">IF($H67="",$G67,$H67)</f>
         <v>艮</v>
       </c>
       <c r="O67" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="O67:O130" si="13">M67&amp;N67</f>
+        <v>䷳艮</v>
+      </c>
+      <c r="P67" t="str">
+        <f t="shared" si="9"/>
         <v>䷳</v>
       </c>
     </row>
-    <row r="68" spans="1:15">
+    <row r="68" spans="1:16">
       <c r="B68" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4DF4</v>
       </c>
       <c r="C68" cm="1">
@@ -12552,7 +12816,7 @@
         <v>53</v>
       </c>
       <c r="F68" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷴</v>
       </c>
       <c r="G68" t="s">
@@ -12571,25 +12835,29 @@
         <v>778788</v>
       </c>
       <c r="L68" t="str">
+        <f t="shared" si="11"/>
+        <v>⚊⚊⚋⚊⚋⚋</v>
+      </c>
+      <c r="M68" t="str">
+        <f t="shared" si="9"/>
+        <v>䷴</v>
+      </c>
+      <c r="N68" t="str">
+        <f t="shared" si="12"/>
+        <v>漸</v>
+      </c>
+      <c r="O68" t="str">
+        <f t="shared" si="13"/>
+        <v>䷴漸</v>
+      </c>
+      <c r="P68" t="str">
+        <f t="shared" si="9"/>
+        <v>䷴</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16">
+      <c r="B69" t="str">
         <f t="shared" si="10"/>
-        <v>⚊⚊⚋⚊⚋⚋</v>
-      </c>
-      <c r="M68" t="str">
-        <f t="shared" si="8"/>
-        <v>䷴</v>
-      </c>
-      <c r="N68" t="str">
-        <f t="shared" si="11"/>
-        <v>漸</v>
-      </c>
-      <c r="O68" t="str">
-        <f t="shared" si="8"/>
-        <v>䷴</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15">
-      <c r="B69" t="str">
-        <f t="shared" si="9"/>
         <v>4DF5</v>
       </c>
       <c r="C69" cm="1">
@@ -12603,7 +12871,7 @@
         <v>54</v>
       </c>
       <c r="F69" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷵</v>
       </c>
       <c r="G69" t="s">
@@ -12622,25 +12890,29 @@
         <v>887877</v>
       </c>
       <c r="L69" t="str">
+        <f t="shared" si="11"/>
+        <v>⚋⚋⚊⚋⚊⚊</v>
+      </c>
+      <c r="M69" t="str">
+        <f t="shared" si="9"/>
+        <v>䷵</v>
+      </c>
+      <c r="N69" t="str">
+        <f t="shared" si="12"/>
+        <v>歸妹</v>
+      </c>
+      <c r="O69" t="str">
+        <f t="shared" si="13"/>
+        <v>䷵歸妹</v>
+      </c>
+      <c r="P69" t="str">
+        <f t="shared" si="9"/>
+        <v>䷵</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16">
+      <c r="B70" t="str">
         <f t="shared" si="10"/>
-        <v>⚋⚋⚊⚋⚊⚊</v>
-      </c>
-      <c r="M69" t="str">
-        <f t="shared" si="8"/>
-        <v>䷵</v>
-      </c>
-      <c r="N69" t="str">
-        <f t="shared" si="11"/>
-        <v>歸妹</v>
-      </c>
-      <c r="O69" t="str">
-        <f t="shared" si="8"/>
-        <v>䷵</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15">
-      <c r="B70" t="str">
-        <f t="shared" si="9"/>
         <v>4DF6</v>
       </c>
       <c r="C70" cm="1">
@@ -12654,7 +12926,7 @@
         <v>55</v>
       </c>
       <c r="F70" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷶</v>
       </c>
       <c r="G70" t="s">
@@ -12673,25 +12945,29 @@
         <v>887787</v>
       </c>
       <c r="L70" t="str">
+        <f t="shared" si="11"/>
+        <v>⚋⚋⚊⚊⚋⚊</v>
+      </c>
+      <c r="M70" t="str">
+        <f t="shared" si="9"/>
+        <v>䷶</v>
+      </c>
+      <c r="N70" t="str">
+        <f t="shared" si="12"/>
+        <v>豐</v>
+      </c>
+      <c r="O70" t="str">
+        <f t="shared" si="13"/>
+        <v>䷶豐</v>
+      </c>
+      <c r="P70" t="str">
+        <f t="shared" si="9"/>
+        <v>䷶</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16">
+      <c r="B71" t="str">
         <f t="shared" si="10"/>
-        <v>⚋⚋⚊⚊⚋⚊</v>
-      </c>
-      <c r="M70" t="str">
-        <f t="shared" si="8"/>
-        <v>䷶</v>
-      </c>
-      <c r="N70" t="str">
-        <f t="shared" si="11"/>
-        <v>豐</v>
-      </c>
-      <c r="O70" t="str">
-        <f t="shared" si="8"/>
-        <v>䷶</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15">
-      <c r="B71" t="str">
-        <f t="shared" si="9"/>
         <v>4DF7</v>
       </c>
       <c r="C71" cm="1">
@@ -12705,7 +12981,7 @@
         <v>56</v>
       </c>
       <c r="F71" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷷</v>
       </c>
       <c r="G71" t="s">
@@ -12724,25 +13000,29 @@
         <v>787788</v>
       </c>
       <c r="L71" t="str">
+        <f t="shared" si="11"/>
+        <v>⚊⚋⚊⚊⚋⚋</v>
+      </c>
+      <c r="M71" t="str">
+        <f t="shared" si="9"/>
+        <v>䷷</v>
+      </c>
+      <c r="N71" t="str">
+        <f t="shared" si="12"/>
+        <v>旅</v>
+      </c>
+      <c r="O71" t="str">
+        <f t="shared" si="13"/>
+        <v>䷷旅</v>
+      </c>
+      <c r="P71" t="str">
+        <f t="shared" si="9"/>
+        <v>䷷</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16">
+      <c r="B72" t="str">
         <f t="shared" si="10"/>
-        <v>⚊⚋⚊⚊⚋⚋</v>
-      </c>
-      <c r="M71" t="str">
-        <f t="shared" si="8"/>
-        <v>䷷</v>
-      </c>
-      <c r="N71" t="str">
-        <f t="shared" si="11"/>
-        <v>旅</v>
-      </c>
-      <c r="O71" t="str">
-        <f t="shared" si="8"/>
-        <v>䷷</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15">
-      <c r="B72" t="str">
-        <f t="shared" si="9"/>
         <v>4DF8</v>
       </c>
       <c r="C72" cm="1">
@@ -12756,7 +13036,7 @@
         <v>57</v>
       </c>
       <c r="F72" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷸</v>
       </c>
       <c r="G72" t="s">
@@ -12775,25 +13055,29 @@
         <v>778778</v>
       </c>
       <c r="L72" t="str">
+        <f t="shared" si="11"/>
+        <v>⚊⚊⚋⚊⚊⚋</v>
+      </c>
+      <c r="M72" t="str">
+        <f t="shared" si="9"/>
+        <v>䷸</v>
+      </c>
+      <c r="N72" t="str">
+        <f t="shared" si="12"/>
+        <v>巽</v>
+      </c>
+      <c r="O72" t="str">
+        <f t="shared" si="13"/>
+        <v>䷸巽</v>
+      </c>
+      <c r="P72" t="str">
+        <f t="shared" si="9"/>
+        <v>䷸</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16">
+      <c r="B73" t="str">
         <f t="shared" si="10"/>
-        <v>⚊⚊⚋⚊⚊⚋</v>
-      </c>
-      <c r="M72" t="str">
-        <f t="shared" si="8"/>
-        <v>䷸</v>
-      </c>
-      <c r="N72" t="str">
-        <f t="shared" si="11"/>
-        <v>巽</v>
-      </c>
-      <c r="O72" t="str">
-        <f t="shared" si="8"/>
-        <v>䷸</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15">
-      <c r="B73" t="str">
-        <f t="shared" si="9"/>
         <v>4DF9</v>
       </c>
       <c r="C73" cm="1">
@@ -12807,7 +13091,7 @@
         <v>58</v>
       </c>
       <c r="F73" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷹</v>
       </c>
       <c r="G73" t="s">
@@ -12826,25 +13110,29 @@
         <v>877877</v>
       </c>
       <c r="L73" t="str">
+        <f t="shared" si="11"/>
+        <v>⚋⚊⚊⚋⚊⚊</v>
+      </c>
+      <c r="M73" t="str">
+        <f t="shared" si="9"/>
+        <v>䷹</v>
+      </c>
+      <c r="N73" t="str">
+        <f t="shared" si="12"/>
+        <v>兌</v>
+      </c>
+      <c r="O73" t="str">
+        <f t="shared" si="13"/>
+        <v>䷹兌</v>
+      </c>
+      <c r="P73" t="str">
+        <f t="shared" si="9"/>
+        <v>䷹</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16">
+      <c r="B74" t="str">
         <f t="shared" si="10"/>
-        <v>⚋⚊⚊⚋⚊⚊</v>
-      </c>
-      <c r="M73" t="str">
-        <f t="shared" si="8"/>
-        <v>䷹</v>
-      </c>
-      <c r="N73" t="str">
-        <f t="shared" si="11"/>
-        <v>兌</v>
-      </c>
-      <c r="O73" t="str">
-        <f t="shared" si="8"/>
-        <v>䷹</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15">
-      <c r="B74" t="str">
-        <f t="shared" si="9"/>
         <v>4DFA</v>
       </c>
       <c r="C74" cm="1">
@@ -12858,7 +13146,7 @@
         <v>59</v>
       </c>
       <c r="F74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷺</v>
       </c>
       <c r="G74" t="s">
@@ -12877,25 +13165,29 @@
         <v>778878</v>
       </c>
       <c r="L74" t="str">
+        <f t="shared" si="11"/>
+        <v>⚊⚊⚋⚋⚊⚋</v>
+      </c>
+      <c r="M74" t="str">
+        <f t="shared" si="9"/>
+        <v>䷺</v>
+      </c>
+      <c r="N74" t="str">
+        <f t="shared" si="12"/>
+        <v>渙</v>
+      </c>
+      <c r="O74" t="str">
+        <f t="shared" si="13"/>
+        <v>䷺渙</v>
+      </c>
+      <c r="P74" t="str">
+        <f t="shared" si="9"/>
+        <v>䷺</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16">
+      <c r="B75" t="str">
         <f t="shared" si="10"/>
-        <v>⚊⚊⚋⚋⚊⚋</v>
-      </c>
-      <c r="M74" t="str">
-        <f t="shared" si="8"/>
-        <v>䷺</v>
-      </c>
-      <c r="N74" t="str">
-        <f t="shared" si="11"/>
-        <v>渙</v>
-      </c>
-      <c r="O74" t="str">
-        <f t="shared" si="8"/>
-        <v>䷺</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15">
-      <c r="B75" t="str">
-        <f t="shared" si="9"/>
         <v>4DFB</v>
       </c>
       <c r="C75" cm="1">
@@ -12909,7 +13201,7 @@
         <v>60</v>
       </c>
       <c r="F75" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷻</v>
       </c>
       <c r="G75" t="s">
@@ -12928,25 +13220,29 @@
         <v>878877</v>
       </c>
       <c r="L75" t="str">
+        <f t="shared" si="11"/>
+        <v>⚋⚊⚋⚋⚊⚊</v>
+      </c>
+      <c r="M75" t="str">
+        <f t="shared" si="9"/>
+        <v>䷻</v>
+      </c>
+      <c r="N75" t="str">
+        <f t="shared" si="12"/>
+        <v>節</v>
+      </c>
+      <c r="O75" t="str">
+        <f t="shared" si="13"/>
+        <v>䷻節</v>
+      </c>
+      <c r="P75" t="str">
+        <f t="shared" si="9"/>
+        <v>䷻</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16">
+      <c r="B76" t="str">
         <f t="shared" si="10"/>
-        <v>⚋⚊⚋⚋⚊⚊</v>
-      </c>
-      <c r="M75" t="str">
-        <f t="shared" si="8"/>
-        <v>䷻</v>
-      </c>
-      <c r="N75" t="str">
-        <f t="shared" si="11"/>
-        <v>節</v>
-      </c>
-      <c r="O75" t="str">
-        <f t="shared" si="8"/>
-        <v>䷻</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15">
-      <c r="B76" t="str">
-        <f t="shared" si="9"/>
         <v>4DFC</v>
       </c>
       <c r="C76" cm="1">
@@ -12960,7 +13256,7 @@
         <v>61</v>
       </c>
       <c r="F76" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷼</v>
       </c>
       <c r="G76" t="s">
@@ -12979,25 +13275,29 @@
         <v>778877</v>
       </c>
       <c r="L76" t="str">
+        <f t="shared" si="11"/>
+        <v>⚊⚊⚋⚋⚊⚊</v>
+      </c>
+      <c r="M76" t="str">
+        <f t="shared" si="9"/>
+        <v>䷼</v>
+      </c>
+      <c r="N76" t="str">
+        <f t="shared" si="12"/>
+        <v>中孚</v>
+      </c>
+      <c r="O76" t="str">
+        <f t="shared" si="13"/>
+        <v>䷼中孚</v>
+      </c>
+      <c r="P76" t="str">
+        <f t="shared" si="9"/>
+        <v>䷼</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16">
+      <c r="B77" t="str">
         <f t="shared" si="10"/>
-        <v>⚊⚊⚋⚋⚊⚊</v>
-      </c>
-      <c r="M76" t="str">
-        <f t="shared" si="8"/>
-        <v>䷼</v>
-      </c>
-      <c r="N76" t="str">
-        <f t="shared" si="11"/>
-        <v>中孚</v>
-      </c>
-      <c r="O76" t="str">
-        <f t="shared" si="8"/>
-        <v>䷼</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15">
-      <c r="B77" t="str">
-        <f t="shared" si="9"/>
         <v>4DFD</v>
       </c>
       <c r="C77" cm="1">
@@ -13011,7 +13311,7 @@
         <v>62</v>
       </c>
       <c r="F77" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷽</v>
       </c>
       <c r="G77" t="s">
@@ -13030,25 +13330,29 @@
         <v>887788</v>
       </c>
       <c r="L77" t="str">
+        <f t="shared" si="11"/>
+        <v>⚋⚋⚊⚊⚋⚋</v>
+      </c>
+      <c r="M77" t="str">
+        <f t="shared" si="9"/>
+        <v>䷽</v>
+      </c>
+      <c r="N77" t="str">
+        <f t="shared" si="12"/>
+        <v>小過</v>
+      </c>
+      <c r="O77" t="str">
+        <f t="shared" si="13"/>
+        <v>䷽小過</v>
+      </c>
+      <c r="P77" t="str">
+        <f t="shared" si="9"/>
+        <v>䷽</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16">
+      <c r="B78" t="str">
         <f t="shared" si="10"/>
-        <v>⚋⚋⚊⚊⚋⚋</v>
-      </c>
-      <c r="M77" t="str">
-        <f t="shared" si="8"/>
-        <v>䷽</v>
-      </c>
-      <c r="N77" t="str">
-        <f t="shared" si="11"/>
-        <v>小過</v>
-      </c>
-      <c r="O77" t="str">
-        <f t="shared" si="8"/>
-        <v>䷽</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15">
-      <c r="B78" t="str">
-        <f t="shared" si="9"/>
         <v>4DFE</v>
       </c>
       <c r="C78" cm="1">
@@ -13062,7 +13366,7 @@
         <v>63</v>
       </c>
       <c r="F78" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷾</v>
       </c>
       <c r="G78" t="s">
@@ -13081,25 +13385,29 @@
         <v>878787</v>
       </c>
       <c r="L78" t="str">
+        <f t="shared" si="11"/>
+        <v>⚋⚊⚋⚊⚋⚊</v>
+      </c>
+      <c r="M78" t="str">
+        <f t="shared" si="9"/>
+        <v>䷾</v>
+      </c>
+      <c r="N78" t="str">
+        <f t="shared" si="12"/>
+        <v>旣濟</v>
+      </c>
+      <c r="O78" t="str">
+        <f t="shared" si="13"/>
+        <v>䷾旣濟</v>
+      </c>
+      <c r="P78" t="str">
+        <f t="shared" si="9"/>
+        <v>䷾</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16">
+      <c r="B79" t="str">
         <f t="shared" si="10"/>
-        <v>⚋⚊⚋⚊⚋⚊</v>
-      </c>
-      <c r="M78" t="str">
-        <f t="shared" si="8"/>
-        <v>䷾</v>
-      </c>
-      <c r="N78" t="str">
-        <f t="shared" si="11"/>
-        <v>旣濟</v>
-      </c>
-      <c r="O78" t="str">
-        <f t="shared" si="8"/>
-        <v>䷾</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15">
-      <c r="B79" t="str">
-        <f t="shared" si="9"/>
         <v>4DFF</v>
       </c>
       <c r="C79" cm="1">
@@ -13113,7 +13421,7 @@
         <v>64</v>
       </c>
       <c r="F79" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>䷿</v>
       </c>
       <c r="G79" t="s">
@@ -13132,28 +13440,32 @@
         <v>787878</v>
       </c>
       <c r="L79" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>⚊⚋⚊⚋⚊⚋</v>
       </c>
       <c r="M79" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>䷿</v>
       </c>
       <c r="N79" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>未濟</v>
       </c>
       <c r="O79" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
+        <v>䷿未濟</v>
+      </c>
+      <c r="P79" t="str">
+        <f t="shared" si="9"/>
         <v>䷿</v>
       </c>
     </row>
-    <row r="80" spans="1:15">
+    <row r="80" spans="1:16">
       <c r="A80" t="s">
         <v>1</v>
       </c>
       <c r="B80" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D300</v>
       </c>
       <c r="C80" cm="1">
@@ -13167,7 +13479,7 @@
         <v>3</v>
       </c>
       <c r="F80" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌀</v>
       </c>
       <c r="H80" t="s">
@@ -13186,25 +13498,29 @@
         <v>9</v>
       </c>
       <c r="L80" t="str">
+        <f t="shared" si="11"/>
+        <v>𝌀</v>
+      </c>
+      <c r="M80" t="str">
+        <f t="shared" si="9"/>
+        <v>𝌀</v>
+      </c>
+      <c r="N80" t="str">
+        <f t="shared" si="12"/>
+        <v>人</v>
+      </c>
+      <c r="O80" t="str">
+        <f t="shared" si="13"/>
+        <v>𝌀人</v>
+      </c>
+      <c r="P80" t="str">
+        <f t="shared" si="9"/>
+        <v>𝌀</v>
+      </c>
+    </row>
+    <row r="81" spans="2:16">
+      <c r="B81" t="str">
         <f t="shared" si="10"/>
-        <v>𝌀</v>
-      </c>
-      <c r="M80" t="str">
-        <f t="shared" si="8"/>
-        <v>𝌀</v>
-      </c>
-      <c r="N80" t="str">
-        <f t="shared" si="11"/>
-        <v>人</v>
-      </c>
-      <c r="O80" t="str">
-        <f t="shared" si="8"/>
-        <v>𝌀</v>
-      </c>
-    </row>
-    <row r="81" spans="2:15">
-      <c r="B81" t="str">
-        <f t="shared" si="9"/>
         <v>1D301</v>
       </c>
       <c r="C81" cm="1">
@@ -13218,7 +13534,7 @@
         <v>5</v>
       </c>
       <c r="F81" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌁</v>
       </c>
       <c r="H81" t="s">
@@ -13240,25 +13556,29 @@
         <v>79</v>
       </c>
       <c r="L81" t="str">
+        <f t="shared" si="11"/>
+        <v>⚊𝌀</v>
+      </c>
+      <c r="M81" t="str">
+        <f t="shared" si="9"/>
+        <v>𝌁</v>
+      </c>
+      <c r="N81" t="str">
+        <f t="shared" si="12"/>
+        <v>天人</v>
+      </c>
+      <c r="O81" t="str">
+        <f t="shared" si="13"/>
+        <v>𝌁天人</v>
+      </c>
+      <c r="P81" t="str">
+        <f t="shared" si="9"/>
+        <v>𝌁</v>
+      </c>
+    </row>
+    <row r="82" spans="2:16">
+      <c r="B82" t="str">
         <f t="shared" si="10"/>
-        <v>⚊𝌀</v>
-      </c>
-      <c r="M81" t="str">
-        <f t="shared" si="8"/>
-        <v>𝌁</v>
-      </c>
-      <c r="N81" t="str">
-        <f t="shared" si="11"/>
-        <v>天人</v>
-      </c>
-      <c r="O81" t="str">
-        <f t="shared" si="8"/>
-        <v>𝌁</v>
-      </c>
-    </row>
-    <row r="82" spans="2:15">
-      <c r="B82" t="str">
-        <f t="shared" si="9"/>
         <v>1D302</v>
       </c>
       <c r="C82" cm="1">
@@ -13272,7 +13592,7 @@
         <v>6</v>
       </c>
       <c r="F82" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌂</v>
       </c>
       <c r="H82" t="s">
@@ -13294,25 +13614,29 @@
         <v>89</v>
       </c>
       <c r="L82" t="str">
+        <f t="shared" si="11"/>
+        <v>⚋𝌀</v>
+      </c>
+      <c r="M82" t="str">
+        <f t="shared" ref="M82:P97" si="14">_xlfn.UNICHAR($C82)</f>
+        <v>𝌂</v>
+      </c>
+      <c r="N82" t="str">
+        <f t="shared" si="12"/>
+        <v>地人</v>
+      </c>
+      <c r="O82" t="str">
+        <f t="shared" si="13"/>
+        <v>𝌂地人</v>
+      </c>
+      <c r="P82" t="str">
+        <f t="shared" si="14"/>
+        <v>𝌂</v>
+      </c>
+    </row>
+    <row r="83" spans="2:16">
+      <c r="B83" t="str">
         <f t="shared" si="10"/>
-        <v>⚋𝌀</v>
-      </c>
-      <c r="M82" t="str">
-        <f t="shared" ref="M82:O97" si="12">_xlfn.UNICHAR($C82)</f>
-        <v>𝌂</v>
-      </c>
-      <c r="N82" t="str">
-        <f t="shared" si="11"/>
-        <v>地人</v>
-      </c>
-      <c r="O82" t="str">
-        <f t="shared" si="12"/>
-        <v>𝌂</v>
-      </c>
-    </row>
-    <row r="83" spans="2:15">
-      <c r="B83" t="str">
-        <f t="shared" si="9"/>
         <v>1D303</v>
       </c>
       <c r="C83" cm="1">
@@ -13326,7 +13650,7 @@
         <v>7</v>
       </c>
       <c r="F83" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌃</v>
       </c>
       <c r="H83" t="s">
@@ -13348,25 +13672,29 @@
         <v>97</v>
       </c>
       <c r="L83" t="str">
+        <f t="shared" si="11"/>
+        <v>𝌀⚊</v>
+      </c>
+      <c r="M83" t="str">
+        <f t="shared" si="14"/>
+        <v>𝌃</v>
+      </c>
+      <c r="N83" t="str">
+        <f t="shared" si="12"/>
+        <v>人天</v>
+      </c>
+      <c r="O83" t="str">
+        <f t="shared" si="13"/>
+        <v>𝌃人天</v>
+      </c>
+      <c r="P83" t="str">
+        <f t="shared" si="14"/>
+        <v>𝌃</v>
+      </c>
+    </row>
+    <row r="84" spans="2:16">
+      <c r="B84" t="str">
         <f t="shared" si="10"/>
-        <v>𝌀⚊</v>
-      </c>
-      <c r="M83" t="str">
-        <f t="shared" si="12"/>
-        <v>𝌃</v>
-      </c>
-      <c r="N83" t="str">
-        <f t="shared" si="11"/>
-        <v>人天</v>
-      </c>
-      <c r="O83" t="str">
-        <f t="shared" si="12"/>
-        <v>𝌃</v>
-      </c>
-    </row>
-    <row r="84" spans="2:15">
-      <c r="B84" t="str">
-        <f t="shared" si="9"/>
         <v>1D304</v>
       </c>
       <c r="C84" cm="1">
@@ -13380,7 +13708,7 @@
         <v>8</v>
       </c>
       <c r="F84" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌄</v>
       </c>
       <c r="H84" t="s">
@@ -13399,25 +13727,29 @@
         <v>98</v>
       </c>
       <c r="L84" t="str">
+        <f t="shared" si="11"/>
+        <v>𝌀⚋</v>
+      </c>
+      <c r="M84" t="str">
+        <f t="shared" si="14"/>
+        <v>𝌄</v>
+      </c>
+      <c r="N84" t="str">
+        <f t="shared" si="12"/>
+        <v>人地</v>
+      </c>
+      <c r="O84" t="str">
+        <f t="shared" si="13"/>
+        <v>𝌄人地</v>
+      </c>
+      <c r="P84" t="str">
+        <f t="shared" si="14"/>
+        <v>𝌄</v>
+      </c>
+    </row>
+    <row r="85" spans="2:16">
+      <c r="B85" t="str">
         <f t="shared" si="10"/>
-        <v>𝌀⚋</v>
-      </c>
-      <c r="M84" t="str">
-        <f t="shared" si="12"/>
-        <v>𝌄</v>
-      </c>
-      <c r="N84" t="str">
-        <f t="shared" si="11"/>
-        <v>人地</v>
-      </c>
-      <c r="O84" t="str">
-        <f t="shared" si="12"/>
-        <v>𝌄</v>
-      </c>
-    </row>
-    <row r="85" spans="2:15">
-      <c r="B85" t="str">
-        <f t="shared" si="9"/>
         <v>1D305</v>
       </c>
       <c r="C85" cm="1">
@@ -13431,7 +13763,7 @@
         <v>9</v>
       </c>
       <c r="F85" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌅</v>
       </c>
       <c r="H85" t="s">
@@ -13450,25 +13782,29 @@
         <v>99</v>
       </c>
       <c r="L85" t="str">
+        <f t="shared" si="11"/>
+        <v>𝌀𝌀</v>
+      </c>
+      <c r="M85" t="str">
+        <f t="shared" si="14"/>
+        <v>𝌅</v>
+      </c>
+      <c r="N85" t="str">
+        <f t="shared" si="12"/>
+        <v>人人</v>
+      </c>
+      <c r="O85" t="str">
+        <f t="shared" si="13"/>
+        <v>𝌅人人</v>
+      </c>
+      <c r="P85" t="str">
+        <f t="shared" si="14"/>
+        <v>𝌅</v>
+      </c>
+    </row>
+    <row r="86" spans="2:16">
+      <c r="B86" t="str">
         <f t="shared" si="10"/>
-        <v>𝌀𝌀</v>
-      </c>
-      <c r="M85" t="str">
-        <f t="shared" si="12"/>
-        <v>𝌅</v>
-      </c>
-      <c r="N85" t="str">
-        <f t="shared" si="11"/>
-        <v>人人</v>
-      </c>
-      <c r="O85" t="str">
-        <f t="shared" si="12"/>
-        <v>𝌅</v>
-      </c>
-    </row>
-    <row r="86" spans="2:15">
-      <c r="B86" t="str">
-        <f t="shared" si="9"/>
         <v>1D306</v>
       </c>
       <c r="C86" cm="1">
@@ -13482,7 +13818,7 @@
         <v>1</v>
       </c>
       <c r="F86" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌆</v>
       </c>
       <c r="H86" t="s">
@@ -13514,21 +13850,25 @@
         <v>⚊⚊⚊⚊</v>
       </c>
       <c r="M86" t="str">
+        <f t="shared" si="14"/>
+        <v>𝌆</v>
+      </c>
+      <c r="N86" t="str">
         <f t="shared" si="12"/>
+        <v>中</v>
+      </c>
+      <c r="O86" t="str">
+        <f t="shared" si="13"/>
+        <v>𝌆中</v>
+      </c>
+      <c r="P86" t="str">
+        <f t="shared" si="14"/>
         <v>𝌆</v>
       </c>
-      <c r="N86" t="str">
-        <f t="shared" si="11"/>
-        <v>中</v>
-      </c>
-      <c r="O86" t="str">
-        <f t="shared" si="12"/>
-        <v>𝌆</v>
-      </c>
-    </row>
-    <row r="87" spans="2:15">
+    </row>
+    <row r="87" spans="2:16">
       <c r="B87" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D307</v>
       </c>
       <c r="C87" cm="1">
@@ -13542,7 +13882,7 @@
         <v>2</v>
       </c>
       <c r="F87" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌇</v>
       </c>
       <c r="H87" t="s">
@@ -13570,25 +13910,29 @@
         <v>7778</v>
       </c>
       <c r="L87" t="str">
-        <f t="shared" ref="L87:L150" si="13">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TEXT($J87,"0"),"1","⚊"),"2","⚋"),"3","𝌀")</f>
+        <f t="shared" ref="L87:L150" si="15">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TEXT($J87,"0"),"1","⚊"),"2","⚋"),"3","𝌀")</f>
         <v>⚊⚊⚊⚋</v>
       </c>
       <c r="M87" t="str">
+        <f t="shared" si="14"/>
+        <v>𝌇</v>
+      </c>
+      <c r="N87" t="str">
         <f t="shared" si="12"/>
+        <v>周</v>
+      </c>
+      <c r="O87" t="str">
+        <f t="shared" si="13"/>
+        <v>𝌇周</v>
+      </c>
+      <c r="P87" t="str">
+        <f t="shared" si="14"/>
         <v>𝌇</v>
       </c>
-      <c r="N87" t="str">
-        <f t="shared" si="11"/>
-        <v>周</v>
-      </c>
-      <c r="O87" t="str">
-        <f t="shared" si="12"/>
-        <v>𝌇</v>
-      </c>
-    </row>
-    <row r="88" spans="2:15">
+    </row>
+    <row r="88" spans="2:16">
       <c r="B88" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D308</v>
       </c>
       <c r="C88" cm="1">
@@ -13602,7 +13946,7 @@
         <v>3</v>
       </c>
       <c r="F88" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌈</v>
       </c>
       <c r="H88" t="s">
@@ -13630,25 +13974,29 @@
         <v>7779</v>
       </c>
       <c r="L88" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊⚊⚊𝌀</v>
+      </c>
+      <c r="M88" t="str">
+        <f t="shared" si="14"/>
+        <v>𝌈</v>
+      </c>
+      <c r="N88" t="str">
+        <f t="shared" si="12"/>
+        <v>礥</v>
+      </c>
+      <c r="O88" t="str">
         <f t="shared" si="13"/>
-        <v>⚊⚊⚊𝌀</v>
-      </c>
-      <c r="M88" t="str">
-        <f t="shared" si="12"/>
+        <v>𝌈礥</v>
+      </c>
+      <c r="P88" t="str">
+        <f t="shared" si="14"/>
         <v>𝌈</v>
       </c>
-      <c r="N88" t="str">
-        <f t="shared" si="11"/>
-        <v>礥</v>
-      </c>
-      <c r="O88" t="str">
-        <f t="shared" si="12"/>
-        <v>𝌈</v>
-      </c>
-    </row>
-    <row r="89" spans="2:15">
+    </row>
+    <row r="89" spans="2:16">
       <c r="B89" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D309</v>
       </c>
       <c r="C89" cm="1">
@@ -13662,7 +14010,7 @@
         <v>4</v>
       </c>
       <c r="F89" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌉</v>
       </c>
       <c r="H89" t="s">
@@ -13690,25 +14038,29 @@
         <v>7787</v>
       </c>
       <c r="L89" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊⚊⚋⚊</v>
+      </c>
+      <c r="M89" t="str">
+        <f t="shared" si="14"/>
+        <v>𝌉</v>
+      </c>
+      <c r="N89" t="str">
+        <f t="shared" si="12"/>
+        <v>閑</v>
+      </c>
+      <c r="O89" t="str">
         <f t="shared" si="13"/>
-        <v>⚊⚊⚋⚊</v>
-      </c>
-      <c r="M89" t="str">
-        <f t="shared" si="12"/>
+        <v>𝌉閑</v>
+      </c>
+      <c r="P89" t="str">
+        <f t="shared" si="14"/>
         <v>𝌉</v>
       </c>
-      <c r="N89" t="str">
-        <f t="shared" si="11"/>
-        <v>閑</v>
-      </c>
-      <c r="O89" t="str">
-        <f t="shared" si="12"/>
-        <v>𝌉</v>
-      </c>
-    </row>
-    <row r="90" spans="2:15">
+    </row>
+    <row r="90" spans="2:16">
       <c r="B90" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D30A</v>
       </c>
       <c r="C90" cm="1">
@@ -13722,7 +14074,7 @@
         <v>5</v>
       </c>
       <c r="F90" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌊</v>
       </c>
       <c r="H90" t="s">
@@ -13750,25 +14102,29 @@
         <v>7788</v>
       </c>
       <c r="L90" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊⚊⚋⚋</v>
+      </c>
+      <c r="M90" t="str">
+        <f t="shared" si="14"/>
+        <v>𝌊</v>
+      </c>
+      <c r="N90" t="str">
+        <f t="shared" si="12"/>
+        <v>少</v>
+      </c>
+      <c r="O90" t="str">
         <f t="shared" si="13"/>
-        <v>⚊⚊⚋⚋</v>
-      </c>
-      <c r="M90" t="str">
-        <f t="shared" si="12"/>
+        <v>𝌊少</v>
+      </c>
+      <c r="P90" t="str">
+        <f t="shared" si="14"/>
         <v>𝌊</v>
       </c>
-      <c r="N90" t="str">
-        <f t="shared" si="11"/>
-        <v>少</v>
-      </c>
-      <c r="O90" t="str">
-        <f t="shared" si="12"/>
-        <v>𝌊</v>
-      </c>
-    </row>
-    <row r="91" spans="2:15">
+    </row>
+    <row r="91" spans="2:16">
       <c r="B91" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D30B</v>
       </c>
       <c r="C91" cm="1">
@@ -13782,7 +14138,7 @@
         <v>6</v>
       </c>
       <c r="F91" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌋</v>
       </c>
       <c r="H91" t="s">
@@ -13810,25 +14166,29 @@
         <v>7789</v>
       </c>
       <c r="L91" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊⚊⚋𝌀</v>
+      </c>
+      <c r="M91" t="str">
+        <f t="shared" si="14"/>
+        <v>𝌋</v>
+      </c>
+      <c r="N91" t="str">
+        <f t="shared" si="12"/>
+        <v>戾</v>
+      </c>
+      <c r="O91" t="str">
         <f t="shared" si="13"/>
-        <v>⚊⚊⚋𝌀</v>
-      </c>
-      <c r="M91" t="str">
-        <f t="shared" si="12"/>
+        <v>𝌋戾</v>
+      </c>
+      <c r="P91" t="str">
+        <f t="shared" si="14"/>
         <v>𝌋</v>
       </c>
-      <c r="N91" t="str">
-        <f t="shared" si="11"/>
-        <v>戾</v>
-      </c>
-      <c r="O91" t="str">
-        <f t="shared" si="12"/>
-        <v>𝌋</v>
-      </c>
-    </row>
-    <row r="92" spans="2:15">
+    </row>
+    <row r="92" spans="2:16">
       <c r="B92" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D30C</v>
       </c>
       <c r="C92" cm="1">
@@ -13842,7 +14202,7 @@
         <v>7</v>
       </c>
       <c r="F92" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌌</v>
       </c>
       <c r="H92" t="s">
@@ -13870,25 +14230,29 @@
         <v>7797</v>
       </c>
       <c r="L92" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊⚊𝌀⚊</v>
+      </c>
+      <c r="M92" t="str">
+        <f t="shared" si="14"/>
+        <v>𝌌</v>
+      </c>
+      <c r="N92" t="str">
+        <f t="shared" si="12"/>
+        <v>上</v>
+      </c>
+      <c r="O92" t="str">
         <f t="shared" si="13"/>
-        <v>⚊⚊𝌀⚊</v>
-      </c>
-      <c r="M92" t="str">
-        <f t="shared" si="12"/>
+        <v>𝌌上</v>
+      </c>
+      <c r="P92" t="str">
+        <f t="shared" si="14"/>
         <v>𝌌</v>
       </c>
-      <c r="N92" t="str">
-        <f t="shared" si="11"/>
-        <v>上</v>
-      </c>
-      <c r="O92" t="str">
-        <f t="shared" si="12"/>
-        <v>𝌌</v>
-      </c>
-    </row>
-    <row r="93" spans="2:15">
+    </row>
+    <row r="93" spans="2:16">
       <c r="B93" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D30D</v>
       </c>
       <c r="C93" cm="1">
@@ -13902,7 +14266,7 @@
         <v>8</v>
       </c>
       <c r="F93" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌍</v>
       </c>
       <c r="H93" t="s">
@@ -13930,25 +14294,29 @@
         <v>7798</v>
       </c>
       <c r="L93" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊⚊𝌀⚋</v>
+      </c>
+      <c r="M93" t="str">
+        <f t="shared" si="14"/>
+        <v>𝌍</v>
+      </c>
+      <c r="N93" t="str">
+        <f t="shared" si="12"/>
+        <v>干</v>
+      </c>
+      <c r="O93" t="str">
         <f t="shared" si="13"/>
-        <v>⚊⚊𝌀⚋</v>
-      </c>
-      <c r="M93" t="str">
-        <f t="shared" si="12"/>
+        <v>𝌍干</v>
+      </c>
+      <c r="P93" t="str">
+        <f t="shared" si="14"/>
         <v>𝌍</v>
       </c>
-      <c r="N93" t="str">
-        <f t="shared" si="11"/>
-        <v>干</v>
-      </c>
-      <c r="O93" t="str">
-        <f t="shared" si="12"/>
-        <v>𝌍</v>
-      </c>
-    </row>
-    <row r="94" spans="2:15">
+    </row>
+    <row r="94" spans="2:16">
       <c r="B94" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D30E</v>
       </c>
       <c r="C94" cm="1">
@@ -13962,7 +14330,7 @@
         <v>9</v>
       </c>
       <c r="F94" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌎</v>
       </c>
       <c r="H94" s="1" t="s">
@@ -13991,25 +14359,29 @@
         <v>7799</v>
       </c>
       <c r="L94" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊⚊𝌀𝌀</v>
+      </c>
+      <c r="M94" t="str">
+        <f t="shared" si="14"/>
+        <v>𝌎</v>
+      </c>
+      <c r="N94" t="str">
+        <f t="shared" si="12"/>
+        <v>𤕠</v>
+      </c>
+      <c r="O94" t="str">
         <f t="shared" si="13"/>
-        <v>⚊⚊𝌀𝌀</v>
-      </c>
-      <c r="M94" t="str">
-        <f t="shared" si="12"/>
+        <v>𝌎𤕠</v>
+      </c>
+      <c r="P94" t="str">
+        <f t="shared" si="14"/>
         <v>𝌎</v>
       </c>
-      <c r="N94" t="str">
-        <f t="shared" si="11"/>
-        <v>𤕠</v>
-      </c>
-      <c r="O94" t="str">
-        <f t="shared" si="12"/>
-        <v>𝌎</v>
-      </c>
-    </row>
-    <row r="95" spans="2:15">
+    </row>
+    <row r="95" spans="2:16">
       <c r="B95" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D30F</v>
       </c>
       <c r="C95" cm="1">
@@ -14023,7 +14395,7 @@
         <v>10</v>
       </c>
       <c r="F95" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌏</v>
       </c>
       <c r="H95" t="s">
@@ -14051,25 +14423,29 @@
         <v>7877</v>
       </c>
       <c r="L95" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊⚋⚊⚊</v>
+      </c>
+      <c r="M95" t="str">
+        <f t="shared" si="14"/>
+        <v>𝌏</v>
+      </c>
+      <c r="N95" t="str">
+        <f t="shared" si="12"/>
+        <v>羨</v>
+      </c>
+      <c r="O95" t="str">
         <f t="shared" si="13"/>
-        <v>⚊⚋⚊⚊</v>
-      </c>
-      <c r="M95" t="str">
-        <f t="shared" si="12"/>
+        <v>𝌏羨</v>
+      </c>
+      <c r="P95" t="str">
+        <f t="shared" si="14"/>
         <v>𝌏</v>
       </c>
-      <c r="N95" t="str">
-        <f t="shared" si="11"/>
-        <v>羨</v>
-      </c>
-      <c r="O95" t="str">
-        <f t="shared" si="12"/>
-        <v>𝌏</v>
-      </c>
-    </row>
-    <row r="96" spans="2:15">
+    </row>
+    <row r="96" spans="2:16">
       <c r="B96" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D310</v>
       </c>
       <c r="C96" cm="1">
@@ -14083,7 +14459,7 @@
         <v>11</v>
       </c>
       <c r="F96" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌐</v>
       </c>
       <c r="H96" t="s">
@@ -14111,25 +14487,29 @@
         <v>7878</v>
       </c>
       <c r="L96" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊⚋⚊⚋</v>
+      </c>
+      <c r="M96" t="str">
+        <f t="shared" si="14"/>
+        <v>𝌐</v>
+      </c>
+      <c r="N96" t="str">
+        <f t="shared" si="12"/>
+        <v>差</v>
+      </c>
+      <c r="O96" t="str">
         <f t="shared" si="13"/>
-        <v>⚊⚋⚊⚋</v>
-      </c>
-      <c r="M96" t="str">
-        <f t="shared" si="12"/>
+        <v>𝌐差</v>
+      </c>
+      <c r="P96" t="str">
+        <f t="shared" si="14"/>
         <v>𝌐</v>
       </c>
-      <c r="N96" t="str">
-        <f t="shared" si="11"/>
-        <v>差</v>
-      </c>
-      <c r="O96" t="str">
-        <f t="shared" si="12"/>
-        <v>𝌐</v>
-      </c>
-    </row>
-    <row r="97" spans="2:15">
+    </row>
+    <row r="97" spans="2:16">
       <c r="B97" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D311</v>
       </c>
       <c r="C97" cm="1">
@@ -14143,7 +14523,7 @@
         <v>12</v>
       </c>
       <c r="F97" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌑</v>
       </c>
       <c r="H97" t="s">
@@ -14171,25 +14551,29 @@
         <v>7879</v>
       </c>
       <c r="L97" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊⚋⚊𝌀</v>
+      </c>
+      <c r="M97" t="str">
+        <f t="shared" si="14"/>
+        <v>𝌑</v>
+      </c>
+      <c r="N97" t="str">
+        <f t="shared" si="12"/>
+        <v>童</v>
+      </c>
+      <c r="O97" t="str">
         <f t="shared" si="13"/>
-        <v>⚊⚋⚊𝌀</v>
-      </c>
-      <c r="M97" t="str">
-        <f t="shared" si="12"/>
+        <v>𝌑童</v>
+      </c>
+      <c r="P97" t="str">
+        <f t="shared" si="14"/>
         <v>𝌑</v>
       </c>
-      <c r="N97" t="str">
-        <f t="shared" si="11"/>
-        <v>童</v>
-      </c>
-      <c r="O97" t="str">
-        <f t="shared" si="12"/>
-        <v>𝌑</v>
-      </c>
-    </row>
-    <row r="98" spans="2:15">
+    </row>
+    <row r="98" spans="2:16">
       <c r="B98" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D312</v>
       </c>
       <c r="C98" cm="1">
@@ -14203,7 +14587,7 @@
         <v>13</v>
       </c>
       <c r="F98" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌒</v>
       </c>
       <c r="H98" t="s">
@@ -14231,25 +14615,29 @@
         <v>7887</v>
       </c>
       <c r="L98" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊⚋⚋⚊</v>
+      </c>
+      <c r="M98" t="str">
+        <f t="shared" ref="M98:P113" si="16">_xlfn.UNICHAR($C98)</f>
+        <v>𝌒</v>
+      </c>
+      <c r="N98" t="str">
+        <f t="shared" si="12"/>
+        <v>增</v>
+      </c>
+      <c r="O98" t="str">
         <f t="shared" si="13"/>
-        <v>⚊⚋⚋⚊</v>
-      </c>
-      <c r="M98" t="str">
-        <f t="shared" ref="M98:O113" si="14">_xlfn.UNICHAR($C98)</f>
+        <v>𝌒增</v>
+      </c>
+      <c r="P98" t="str">
+        <f t="shared" si="16"/>
         <v>𝌒</v>
       </c>
-      <c r="N98" t="str">
-        <f t="shared" si="11"/>
-        <v>增</v>
-      </c>
-      <c r="O98" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌒</v>
-      </c>
-    </row>
-    <row r="99" spans="2:15">
+    </row>
+    <row r="99" spans="2:16">
       <c r="B99" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D313</v>
       </c>
       <c r="C99" cm="1">
@@ -14263,7 +14651,7 @@
         <v>14</v>
       </c>
       <c r="F99" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌓</v>
       </c>
       <c r="H99" t="s">
@@ -14291,25 +14679,29 @@
         <v>7888</v>
       </c>
       <c r="L99" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊⚋⚋⚋</v>
+      </c>
+      <c r="M99" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌓</v>
+      </c>
+      <c r="N99" t="str">
+        <f t="shared" si="12"/>
+        <v>銳</v>
+      </c>
+      <c r="O99" t="str">
         <f t="shared" si="13"/>
-        <v>⚊⚋⚋⚋</v>
-      </c>
-      <c r="M99" t="str">
-        <f t="shared" si="14"/>
+        <v>𝌓銳</v>
+      </c>
+      <c r="P99" t="str">
+        <f t="shared" si="16"/>
         <v>𝌓</v>
       </c>
-      <c r="N99" t="str">
-        <f t="shared" si="11"/>
-        <v>銳</v>
-      </c>
-      <c r="O99" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌓</v>
-      </c>
-    </row>
-    <row r="100" spans="2:15">
+    </row>
+    <row r="100" spans="2:16">
       <c r="B100" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D314</v>
       </c>
       <c r="C100" cm="1">
@@ -14323,7 +14715,7 @@
         <v>15</v>
       </c>
       <c r="F100" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌔</v>
       </c>
       <c r="H100" t="s">
@@ -14351,25 +14743,29 @@
         <v>7889</v>
       </c>
       <c r="L100" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊⚋⚋𝌀</v>
+      </c>
+      <c r="M100" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌔</v>
+      </c>
+      <c r="N100" t="str">
+        <f t="shared" si="12"/>
+        <v>達</v>
+      </c>
+      <c r="O100" t="str">
         <f t="shared" si="13"/>
-        <v>⚊⚋⚋𝌀</v>
-      </c>
-      <c r="M100" t="str">
-        <f t="shared" si="14"/>
+        <v>𝌔達</v>
+      </c>
+      <c r="P100" t="str">
+        <f t="shared" si="16"/>
         <v>𝌔</v>
       </c>
-      <c r="N100" t="str">
-        <f t="shared" si="11"/>
-        <v>達</v>
-      </c>
-      <c r="O100" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌔</v>
-      </c>
-    </row>
-    <row r="101" spans="2:15">
+    </row>
+    <row r="101" spans="2:16">
       <c r="B101" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D315</v>
       </c>
       <c r="C101" cm="1">
@@ -14383,7 +14779,7 @@
         <v>16</v>
       </c>
       <c r="F101" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌕</v>
       </c>
       <c r="H101" t="s">
@@ -14411,25 +14807,29 @@
         <v>7897</v>
       </c>
       <c r="L101" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊⚋𝌀⚊</v>
+      </c>
+      <c r="M101" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌕</v>
+      </c>
+      <c r="N101" t="str">
+        <f t="shared" si="12"/>
+        <v>交</v>
+      </c>
+      <c r="O101" t="str">
         <f t="shared" si="13"/>
-        <v>⚊⚋𝌀⚊</v>
-      </c>
-      <c r="M101" t="str">
-        <f t="shared" si="14"/>
+        <v>𝌕交</v>
+      </c>
+      <c r="P101" t="str">
+        <f t="shared" si="16"/>
         <v>𝌕</v>
       </c>
-      <c r="N101" t="str">
-        <f t="shared" si="11"/>
-        <v>交</v>
-      </c>
-      <c r="O101" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌕</v>
-      </c>
-    </row>
-    <row r="102" spans="2:15">
+    </row>
+    <row r="102" spans="2:16">
       <c r="B102" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D316</v>
       </c>
       <c r="C102" cm="1">
@@ -14443,7 +14843,7 @@
         <v>17</v>
       </c>
       <c r="F102" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌖</v>
       </c>
       <c r="H102" t="s">
@@ -14471,25 +14871,29 @@
         <v>7898</v>
       </c>
       <c r="L102" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊⚋𝌀⚋</v>
+      </c>
+      <c r="M102" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌖</v>
+      </c>
+      <c r="N102" t="str">
+        <f t="shared" si="12"/>
+        <v>䎡</v>
+      </c>
+      <c r="O102" t="str">
         <f t="shared" si="13"/>
-        <v>⚊⚋𝌀⚋</v>
-      </c>
-      <c r="M102" t="str">
-        <f t="shared" si="14"/>
+        <v>𝌖䎡</v>
+      </c>
+      <c r="P102" t="str">
+        <f t="shared" si="16"/>
         <v>𝌖</v>
       </c>
-      <c r="N102" t="str">
-        <f t="shared" si="11"/>
-        <v>䎡</v>
-      </c>
-      <c r="O102" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌖</v>
-      </c>
-    </row>
-    <row r="103" spans="2:15">
+    </row>
+    <row r="103" spans="2:16">
       <c r="B103" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D317</v>
       </c>
       <c r="C103" cm="1">
@@ -14503,7 +14907,7 @@
         <v>18</v>
       </c>
       <c r="F103" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌗</v>
       </c>
       <c r="H103" t="s">
@@ -14531,25 +14935,29 @@
         <v>7899</v>
       </c>
       <c r="L103" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊⚋𝌀𝌀</v>
+      </c>
+      <c r="M103" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌗</v>
+      </c>
+      <c r="N103" t="str">
+        <f t="shared" si="12"/>
+        <v>傒</v>
+      </c>
+      <c r="O103" t="str">
         <f t="shared" si="13"/>
-        <v>⚊⚋𝌀𝌀</v>
-      </c>
-      <c r="M103" t="str">
-        <f t="shared" si="14"/>
+        <v>𝌗傒</v>
+      </c>
+      <c r="P103" t="str">
+        <f t="shared" si="16"/>
         <v>𝌗</v>
       </c>
-      <c r="N103" t="str">
-        <f t="shared" si="11"/>
-        <v>傒</v>
-      </c>
-      <c r="O103" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌗</v>
-      </c>
-    </row>
-    <row r="104" spans="2:15">
+    </row>
+    <row r="104" spans="2:16">
       <c r="B104" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D318</v>
       </c>
       <c r="C104" cm="1">
@@ -14563,7 +14971,7 @@
         <v>19</v>
       </c>
       <c r="F104" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌘</v>
       </c>
       <c r="H104" t="s">
@@ -14591,25 +14999,29 @@
         <v>7977</v>
       </c>
       <c r="L104" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊𝌀⚊⚊</v>
+      </c>
+      <c r="M104" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌘</v>
+      </c>
+      <c r="N104" t="str">
+        <f t="shared" si="12"/>
+        <v>從</v>
+      </c>
+      <c r="O104" t="str">
         <f t="shared" si="13"/>
-        <v>⚊𝌀⚊⚊</v>
-      </c>
-      <c r="M104" t="str">
-        <f t="shared" si="14"/>
+        <v>𝌘從</v>
+      </c>
+      <c r="P104" t="str">
+        <f t="shared" si="16"/>
         <v>𝌘</v>
       </c>
-      <c r="N104" t="str">
-        <f t="shared" si="11"/>
-        <v>從</v>
-      </c>
-      <c r="O104" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌘</v>
-      </c>
-    </row>
-    <row r="105" spans="2:15">
+    </row>
+    <row r="105" spans="2:16">
       <c r="B105" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D319</v>
       </c>
       <c r="C105" cm="1">
@@ -14623,7 +15035,7 @@
         <v>20</v>
       </c>
       <c r="F105" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌙</v>
       </c>
       <c r="H105" t="s">
@@ -14651,25 +15063,29 @@
         <v>7978</v>
       </c>
       <c r="L105" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊𝌀⚊⚋</v>
+      </c>
+      <c r="M105" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌙</v>
+      </c>
+      <c r="N105" t="str">
+        <f t="shared" si="12"/>
+        <v>進</v>
+      </c>
+      <c r="O105" t="str">
         <f t="shared" si="13"/>
-        <v>⚊𝌀⚊⚋</v>
-      </c>
-      <c r="M105" t="str">
-        <f t="shared" si="14"/>
+        <v>𝌙進</v>
+      </c>
+      <c r="P105" t="str">
+        <f t="shared" si="16"/>
         <v>𝌙</v>
       </c>
-      <c r="N105" t="str">
-        <f t="shared" si="11"/>
-        <v>進</v>
-      </c>
-      <c r="O105" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌙</v>
-      </c>
-    </row>
-    <row r="106" spans="2:15">
+    </row>
+    <row r="106" spans="2:16">
       <c r="B106" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D31A</v>
       </c>
       <c r="C106" cm="1">
@@ -14683,7 +15099,7 @@
         <v>21</v>
       </c>
       <c r="F106" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌚</v>
       </c>
       <c r="H106" t="s">
@@ -14711,25 +15127,29 @@
         <v>7979</v>
       </c>
       <c r="L106" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊𝌀⚊𝌀</v>
+      </c>
+      <c r="M106" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌚</v>
+      </c>
+      <c r="N106" t="str">
+        <f t="shared" si="12"/>
+        <v>釋</v>
+      </c>
+      <c r="O106" t="str">
         <f t="shared" si="13"/>
-        <v>⚊𝌀⚊𝌀</v>
-      </c>
-      <c r="M106" t="str">
-        <f t="shared" si="14"/>
+        <v>𝌚釋</v>
+      </c>
+      <c r="P106" t="str">
+        <f t="shared" si="16"/>
         <v>𝌚</v>
       </c>
-      <c r="N106" t="str">
-        <f t="shared" si="11"/>
-        <v>釋</v>
-      </c>
-      <c r="O106" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌚</v>
-      </c>
-    </row>
-    <row r="107" spans="2:15">
+    </row>
+    <row r="107" spans="2:16">
       <c r="B107" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D31B</v>
       </c>
       <c r="C107" cm="1">
@@ -14743,7 +15163,7 @@
         <v>22</v>
       </c>
       <c r="F107" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌛</v>
       </c>
       <c r="H107" t="s">
@@ -14771,25 +15191,29 @@
         <v>7987</v>
       </c>
       <c r="L107" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊𝌀⚋⚊</v>
+      </c>
+      <c r="M107" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌛</v>
+      </c>
+      <c r="N107" t="str">
+        <f t="shared" si="12"/>
+        <v>格</v>
+      </c>
+      <c r="O107" t="str">
         <f t="shared" si="13"/>
-        <v>⚊𝌀⚋⚊</v>
-      </c>
-      <c r="M107" t="str">
-        <f t="shared" si="14"/>
+        <v>𝌛格</v>
+      </c>
+      <c r="P107" t="str">
+        <f t="shared" si="16"/>
         <v>𝌛</v>
       </c>
-      <c r="N107" t="str">
-        <f t="shared" si="11"/>
-        <v>格</v>
-      </c>
-      <c r="O107" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌛</v>
-      </c>
-    </row>
-    <row r="108" spans="2:15">
+    </row>
+    <row r="108" spans="2:16">
       <c r="B108" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D31C</v>
       </c>
       <c r="C108" cm="1">
@@ -14803,7 +15227,7 @@
         <v>23</v>
       </c>
       <c r="F108" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌜</v>
       </c>
       <c r="H108" t="s">
@@ -14831,25 +15255,29 @@
         <v>7988</v>
       </c>
       <c r="L108" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊𝌀⚋⚋</v>
+      </c>
+      <c r="M108" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌜</v>
+      </c>
+      <c r="N108" t="str">
+        <f t="shared" si="12"/>
+        <v>夷</v>
+      </c>
+      <c r="O108" t="str">
         <f t="shared" si="13"/>
-        <v>⚊𝌀⚋⚋</v>
-      </c>
-      <c r="M108" t="str">
-        <f t="shared" si="14"/>
+        <v>𝌜夷</v>
+      </c>
+      <c r="P108" t="str">
+        <f t="shared" si="16"/>
         <v>𝌜</v>
       </c>
-      <c r="N108" t="str">
-        <f t="shared" si="11"/>
-        <v>夷</v>
-      </c>
-      <c r="O108" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌜</v>
-      </c>
-    </row>
-    <row r="109" spans="2:15">
+    </row>
+    <row r="109" spans="2:16">
       <c r="B109" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D31D</v>
       </c>
       <c r="C109" cm="1">
@@ -14863,7 +15291,7 @@
         <v>24</v>
       </c>
       <c r="F109" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌝</v>
       </c>
       <c r="H109" t="s">
@@ -14891,25 +15319,29 @@
         <v>7989</v>
       </c>
       <c r="L109" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊𝌀⚋𝌀</v>
+      </c>
+      <c r="M109" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌝</v>
+      </c>
+      <c r="N109" t="str">
+        <f t="shared" si="12"/>
+        <v>樂</v>
+      </c>
+      <c r="O109" t="str">
         <f t="shared" si="13"/>
-        <v>⚊𝌀⚋𝌀</v>
-      </c>
-      <c r="M109" t="str">
-        <f t="shared" si="14"/>
+        <v>𝌝樂</v>
+      </c>
+      <c r="P109" t="str">
+        <f t="shared" si="16"/>
         <v>𝌝</v>
       </c>
-      <c r="N109" t="str">
-        <f t="shared" si="11"/>
-        <v>樂</v>
-      </c>
-      <c r="O109" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌝</v>
-      </c>
-    </row>
-    <row r="110" spans="2:15">
+    </row>
+    <row r="110" spans="2:16">
       <c r="B110" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D31E</v>
       </c>
       <c r="C110" cm="1">
@@ -14923,7 +15355,7 @@
         <v>25</v>
       </c>
       <c r="F110" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌞</v>
       </c>
       <c r="H110" t="s">
@@ -14951,25 +15383,29 @@
         <v>7997</v>
       </c>
       <c r="L110" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊𝌀𝌀⚊</v>
+      </c>
+      <c r="M110" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌞</v>
+      </c>
+      <c r="N110" t="str">
+        <f t="shared" si="12"/>
+        <v>爭</v>
+      </c>
+      <c r="O110" t="str">
         <f t="shared" si="13"/>
-        <v>⚊𝌀𝌀⚊</v>
-      </c>
-      <c r="M110" t="str">
-        <f t="shared" si="14"/>
+        <v>𝌞爭</v>
+      </c>
+      <c r="P110" t="str">
+        <f t="shared" si="16"/>
         <v>𝌞</v>
       </c>
-      <c r="N110" t="str">
-        <f t="shared" si="11"/>
-        <v>爭</v>
-      </c>
-      <c r="O110" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌞</v>
-      </c>
-    </row>
-    <row r="111" spans="2:15">
+    </row>
+    <row r="111" spans="2:16">
       <c r="B111" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D31F</v>
       </c>
       <c r="C111" cm="1">
@@ -14983,7 +15419,7 @@
         <v>26</v>
       </c>
       <c r="F111" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌟</v>
       </c>
       <c r="H111" t="s">
@@ -15011,25 +15447,29 @@
         <v>7998</v>
       </c>
       <c r="L111" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊𝌀𝌀⚋</v>
+      </c>
+      <c r="M111" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌟</v>
+      </c>
+      <c r="N111" t="str">
+        <f t="shared" si="12"/>
+        <v>務</v>
+      </c>
+      <c r="O111" t="str">
         <f t="shared" si="13"/>
-        <v>⚊𝌀𝌀⚋</v>
-      </c>
-      <c r="M111" t="str">
-        <f t="shared" si="14"/>
+        <v>𝌟務</v>
+      </c>
+      <c r="P111" t="str">
+        <f t="shared" si="16"/>
         <v>𝌟</v>
       </c>
-      <c r="N111" t="str">
-        <f t="shared" si="11"/>
-        <v>務</v>
-      </c>
-      <c r="O111" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌟</v>
-      </c>
-    </row>
-    <row r="112" spans="2:15">
+    </row>
+    <row r="112" spans="2:16">
       <c r="B112" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D320</v>
       </c>
       <c r="C112" cm="1">
@@ -15043,7 +15483,7 @@
         <v>27</v>
       </c>
       <c r="F112" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌠</v>
       </c>
       <c r="H112" t="s">
@@ -15071,25 +15511,29 @@
         <v>7999</v>
       </c>
       <c r="L112" t="str">
+        <f t="shared" si="15"/>
+        <v>⚊𝌀𝌀𝌀</v>
+      </c>
+      <c r="M112" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌠</v>
+      </c>
+      <c r="N112" t="str">
+        <f t="shared" si="12"/>
+        <v>事</v>
+      </c>
+      <c r="O112" t="str">
         <f t="shared" si="13"/>
-        <v>⚊𝌀𝌀𝌀</v>
-      </c>
-      <c r="M112" t="str">
-        <f t="shared" si="14"/>
+        <v>𝌠事</v>
+      </c>
+      <c r="P112" t="str">
+        <f t="shared" si="16"/>
         <v>𝌠</v>
       </c>
-      <c r="N112" t="str">
-        <f t="shared" si="11"/>
-        <v>事</v>
-      </c>
-      <c r="O112" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌠</v>
-      </c>
-    </row>
-    <row r="113" spans="2:15">
+    </row>
+    <row r="113" spans="2:16">
       <c r="B113" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D321</v>
       </c>
       <c r="C113" cm="1">
@@ -15103,7 +15547,7 @@
         <v>28</v>
       </c>
       <c r="F113" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌡</v>
       </c>
       <c r="H113" t="s">
@@ -15131,25 +15575,29 @@
         <v>8777</v>
       </c>
       <c r="L113" t="str">
+        <f t="shared" si="15"/>
+        <v>⚋⚊⚊⚊</v>
+      </c>
+      <c r="M113" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌡</v>
+      </c>
+      <c r="N113" t="str">
+        <f t="shared" si="12"/>
+        <v>更</v>
+      </c>
+      <c r="O113" t="str">
         <f t="shared" si="13"/>
-        <v>⚋⚊⚊⚊</v>
-      </c>
-      <c r="M113" t="str">
-        <f t="shared" si="14"/>
+        <v>𝌡更</v>
+      </c>
+      <c r="P113" t="str">
+        <f t="shared" si="16"/>
         <v>𝌡</v>
       </c>
-      <c r="N113" t="str">
-        <f t="shared" si="11"/>
-        <v>更</v>
-      </c>
-      <c r="O113" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌡</v>
-      </c>
-    </row>
-    <row r="114" spans="2:15">
+    </row>
+    <row r="114" spans="2:16">
       <c r="B114" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D322</v>
       </c>
       <c r="C114" cm="1">
@@ -15163,7 +15611,7 @@
         <v>29</v>
       </c>
       <c r="F114" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌢</v>
       </c>
       <c r="H114" t="s">
@@ -15191,25 +15639,29 @@
         <v>8778</v>
       </c>
       <c r="L114" t="str">
+        <f t="shared" si="15"/>
+        <v>⚋⚊⚊⚋</v>
+      </c>
+      <c r="M114" t="str">
+        <f t="shared" ref="M114:P129" si="17">_xlfn.UNICHAR($C114)</f>
+        <v>𝌢</v>
+      </c>
+      <c r="N114" t="str">
+        <f t="shared" si="12"/>
+        <v>斷</v>
+      </c>
+      <c r="O114" t="str">
         <f t="shared" si="13"/>
-        <v>⚋⚊⚊⚋</v>
-      </c>
-      <c r="M114" t="str">
-        <f t="shared" ref="M114:O129" si="15">_xlfn.UNICHAR($C114)</f>
+        <v>𝌢斷</v>
+      </c>
+      <c r="P114" t="str">
+        <f t="shared" si="17"/>
         <v>𝌢</v>
       </c>
-      <c r="N114" t="str">
-        <f t="shared" si="11"/>
-        <v>斷</v>
-      </c>
-      <c r="O114" t="str">
-        <f t="shared" si="15"/>
-        <v>𝌢</v>
-      </c>
-    </row>
-    <row r="115" spans="2:15">
+    </row>
+    <row r="115" spans="2:16">
       <c r="B115" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D323</v>
       </c>
       <c r="C115" cm="1">
@@ -15223,7 +15675,7 @@
         <v>30</v>
       </c>
       <c r="F115" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌣</v>
       </c>
       <c r="H115" t="s">
@@ -15251,25 +15703,29 @@
         <v>8779</v>
       </c>
       <c r="L115" t="str">
+        <f t="shared" si="15"/>
+        <v>⚋⚊⚊𝌀</v>
+      </c>
+      <c r="M115" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌣</v>
+      </c>
+      <c r="N115" t="str">
+        <f t="shared" si="12"/>
+        <v>毅</v>
+      </c>
+      <c r="O115" t="str">
         <f t="shared" si="13"/>
-        <v>⚋⚊⚊𝌀</v>
-      </c>
-      <c r="M115" t="str">
-        <f t="shared" si="15"/>
+        <v>𝌣毅</v>
+      </c>
+      <c r="P115" t="str">
+        <f t="shared" si="17"/>
         <v>𝌣</v>
       </c>
-      <c r="N115" t="str">
-        <f t="shared" si="11"/>
-        <v>毅</v>
-      </c>
-      <c r="O115" t="str">
-        <f t="shared" si="15"/>
-        <v>𝌣</v>
-      </c>
-    </row>
-    <row r="116" spans="2:15">
+    </row>
+    <row r="116" spans="2:16">
       <c r="B116" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D324</v>
       </c>
       <c r="C116" cm="1">
@@ -15283,7 +15739,7 @@
         <v>31</v>
       </c>
       <c r="F116" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌤</v>
       </c>
       <c r="H116" t="s">
@@ -15311,25 +15767,29 @@
         <v>8787</v>
       </c>
       <c r="L116" t="str">
+        <f t="shared" si="15"/>
+        <v>⚋⚊⚋⚊</v>
+      </c>
+      <c r="M116" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌤</v>
+      </c>
+      <c r="N116" t="str">
+        <f t="shared" si="12"/>
+        <v>裝</v>
+      </c>
+      <c r="O116" t="str">
         <f t="shared" si="13"/>
-        <v>⚋⚊⚋⚊</v>
-      </c>
-      <c r="M116" t="str">
-        <f t="shared" si="15"/>
+        <v>𝌤裝</v>
+      </c>
+      <c r="P116" t="str">
+        <f t="shared" si="17"/>
         <v>𝌤</v>
       </c>
-      <c r="N116" t="str">
-        <f t="shared" si="11"/>
-        <v>裝</v>
-      </c>
-      <c r="O116" t="str">
-        <f t="shared" si="15"/>
-        <v>𝌤</v>
-      </c>
-    </row>
-    <row r="117" spans="2:15">
+    </row>
+    <row r="117" spans="2:16">
       <c r="B117" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D325</v>
       </c>
       <c r="C117" cm="1">
@@ -15343,7 +15803,7 @@
         <v>32</v>
       </c>
       <c r="F117" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌥</v>
       </c>
       <c r="H117" t="s">
@@ -15371,25 +15831,29 @@
         <v>8788</v>
       </c>
       <c r="L117" t="str">
+        <f t="shared" si="15"/>
+        <v>⚋⚊⚋⚋</v>
+      </c>
+      <c r="M117" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌥</v>
+      </c>
+      <c r="N117" t="str">
+        <f t="shared" si="12"/>
+        <v>眾</v>
+      </c>
+      <c r="O117" t="str">
         <f t="shared" si="13"/>
-        <v>⚋⚊⚋⚋</v>
-      </c>
-      <c r="M117" t="str">
-        <f t="shared" si="15"/>
+        <v>𝌥眾</v>
+      </c>
+      <c r="P117" t="str">
+        <f t="shared" si="17"/>
         <v>𝌥</v>
       </c>
-      <c r="N117" t="str">
-        <f t="shared" si="11"/>
-        <v>眾</v>
-      </c>
-      <c r="O117" t="str">
-        <f t="shared" si="15"/>
-        <v>𝌥</v>
-      </c>
-    </row>
-    <row r="118" spans="2:15">
+    </row>
+    <row r="118" spans="2:16">
       <c r="B118" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D326</v>
       </c>
       <c r="C118" cm="1">
@@ -15403,7 +15867,7 @@
         <v>33</v>
       </c>
       <c r="F118" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌦</v>
       </c>
       <c r="H118" t="s">
@@ -15431,25 +15895,29 @@
         <v>8789</v>
       </c>
       <c r="L118" t="str">
+        <f t="shared" si="15"/>
+        <v>⚋⚊⚋𝌀</v>
+      </c>
+      <c r="M118" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌦</v>
+      </c>
+      <c r="N118" t="str">
+        <f t="shared" si="12"/>
+        <v>密</v>
+      </c>
+      <c r="O118" t="str">
         <f t="shared" si="13"/>
-        <v>⚋⚊⚋𝌀</v>
-      </c>
-      <c r="M118" t="str">
-        <f t="shared" si="15"/>
+        <v>𝌦密</v>
+      </c>
+      <c r="P118" t="str">
+        <f t="shared" si="17"/>
         <v>𝌦</v>
       </c>
-      <c r="N118" t="str">
-        <f t="shared" si="11"/>
-        <v>密</v>
-      </c>
-      <c r="O118" t="str">
-        <f t="shared" si="15"/>
-        <v>𝌦</v>
-      </c>
-    </row>
-    <row r="119" spans="2:15">
+    </row>
+    <row r="119" spans="2:16">
       <c r="B119" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D327</v>
       </c>
       <c r="C119" cm="1">
@@ -15463,7 +15931,7 @@
         <v>34</v>
       </c>
       <c r="F119" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌧</v>
       </c>
       <c r="H119" t="s">
@@ -15491,25 +15959,29 @@
         <v>8797</v>
       </c>
       <c r="L119" t="str">
+        <f t="shared" si="15"/>
+        <v>⚋⚊𝌀⚊</v>
+      </c>
+      <c r="M119" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌧</v>
+      </c>
+      <c r="N119" t="str">
+        <f t="shared" si="12"/>
+        <v>親</v>
+      </c>
+      <c r="O119" t="str">
         <f t="shared" si="13"/>
-        <v>⚋⚊𝌀⚊</v>
-      </c>
-      <c r="M119" t="str">
-        <f t="shared" si="15"/>
+        <v>𝌧親</v>
+      </c>
+      <c r="P119" t="str">
+        <f t="shared" si="17"/>
         <v>𝌧</v>
       </c>
-      <c r="N119" t="str">
-        <f t="shared" si="11"/>
-        <v>親</v>
-      </c>
-      <c r="O119" t="str">
-        <f t="shared" si="15"/>
-        <v>𝌧</v>
-      </c>
-    </row>
-    <row r="120" spans="2:15">
+    </row>
+    <row r="120" spans="2:16">
       <c r="B120" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D328</v>
       </c>
       <c r="C120" cm="1">
@@ -15523,7 +15995,7 @@
         <v>35</v>
       </c>
       <c r="F120" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌨</v>
       </c>
       <c r="H120" t="s">
@@ -15551,25 +16023,29 @@
         <v>8798</v>
       </c>
       <c r="L120" t="str">
+        <f t="shared" si="15"/>
+        <v>⚋⚊𝌀⚋</v>
+      </c>
+      <c r="M120" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌨</v>
+      </c>
+      <c r="N120" t="str">
+        <f t="shared" si="12"/>
+        <v>斂</v>
+      </c>
+      <c r="O120" t="str">
         <f t="shared" si="13"/>
-        <v>⚋⚊𝌀⚋</v>
-      </c>
-      <c r="M120" t="str">
-        <f t="shared" si="15"/>
+        <v>𝌨斂</v>
+      </c>
+      <c r="P120" t="str">
+        <f t="shared" si="17"/>
         <v>𝌨</v>
       </c>
-      <c r="N120" t="str">
-        <f t="shared" si="11"/>
-        <v>斂</v>
-      </c>
-      <c r="O120" t="str">
-        <f t="shared" si="15"/>
-        <v>𝌨</v>
-      </c>
-    </row>
-    <row r="121" spans="2:15">
+    </row>
+    <row r="121" spans="2:16">
       <c r="B121" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D329</v>
       </c>
       <c r="C121" cm="1">
@@ -15583,7 +16059,7 @@
         <v>36</v>
       </c>
       <c r="F121" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌩</v>
       </c>
       <c r="H121" t="s">
@@ -15611,25 +16087,29 @@
         <v>8799</v>
       </c>
       <c r="L121" t="str">
+        <f t="shared" si="15"/>
+        <v>⚋⚊𝌀𝌀</v>
+      </c>
+      <c r="M121" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌩</v>
+      </c>
+      <c r="N121" t="str">
+        <f t="shared" si="12"/>
+        <v>彊</v>
+      </c>
+      <c r="O121" t="str">
         <f t="shared" si="13"/>
-        <v>⚋⚊𝌀𝌀</v>
-      </c>
-      <c r="M121" t="str">
-        <f t="shared" si="15"/>
+        <v>𝌩彊</v>
+      </c>
+      <c r="P121" t="str">
+        <f t="shared" si="17"/>
         <v>𝌩</v>
       </c>
-      <c r="N121" t="str">
-        <f t="shared" si="11"/>
-        <v>彊</v>
-      </c>
-      <c r="O121" t="str">
-        <f t="shared" si="15"/>
-        <v>𝌩</v>
-      </c>
-    </row>
-    <row r="122" spans="2:15">
+    </row>
+    <row r="122" spans="2:16">
       <c r="B122" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D32A</v>
       </c>
       <c r="C122" cm="1">
@@ -15643,7 +16123,7 @@
         <v>37</v>
       </c>
       <c r="F122" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌪</v>
       </c>
       <c r="H122" t="s">
@@ -15671,25 +16151,29 @@
         <v>8877</v>
       </c>
       <c r="L122" t="str">
+        <f t="shared" si="15"/>
+        <v>⚋⚋⚊⚊</v>
+      </c>
+      <c r="M122" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌪</v>
+      </c>
+      <c r="N122" t="str">
+        <f t="shared" si="12"/>
+        <v>睟</v>
+      </c>
+      <c r="O122" t="str">
         <f t="shared" si="13"/>
-        <v>⚋⚋⚊⚊</v>
-      </c>
-      <c r="M122" t="str">
-        <f t="shared" si="15"/>
+        <v>𝌪睟</v>
+      </c>
+      <c r="P122" t="str">
+        <f t="shared" si="17"/>
         <v>𝌪</v>
       </c>
-      <c r="N122" t="str">
-        <f t="shared" si="11"/>
-        <v>睟</v>
-      </c>
-      <c r="O122" t="str">
-        <f t="shared" si="15"/>
-        <v>𝌪</v>
-      </c>
-    </row>
-    <row r="123" spans="2:15">
+    </row>
+    <row r="123" spans="2:16">
       <c r="B123" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D32B</v>
       </c>
       <c r="C123" cm="1">
@@ -15703,7 +16187,7 @@
         <v>38</v>
       </c>
       <c r="F123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌫</v>
       </c>
       <c r="H123" t="s">
@@ -15731,25 +16215,29 @@
         <v>8878</v>
       </c>
       <c r="L123" t="str">
+        <f t="shared" si="15"/>
+        <v>⚋⚋⚊⚋</v>
+      </c>
+      <c r="M123" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌫</v>
+      </c>
+      <c r="N123" t="str">
+        <f t="shared" si="12"/>
+        <v>盛</v>
+      </c>
+      <c r="O123" t="str">
         <f t="shared" si="13"/>
-        <v>⚋⚋⚊⚋</v>
-      </c>
-      <c r="M123" t="str">
-        <f t="shared" si="15"/>
+        <v>𝌫盛</v>
+      </c>
+      <c r="P123" t="str">
+        <f t="shared" si="17"/>
         <v>𝌫</v>
       </c>
-      <c r="N123" t="str">
-        <f t="shared" si="11"/>
-        <v>盛</v>
-      </c>
-      <c r="O123" t="str">
-        <f t="shared" si="15"/>
-        <v>𝌫</v>
-      </c>
-    </row>
-    <row r="124" spans="2:15">
+    </row>
+    <row r="124" spans="2:16">
       <c r="B124" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D32C</v>
       </c>
       <c r="C124" cm="1">
@@ -15763,7 +16251,7 @@
         <v>39</v>
       </c>
       <c r="F124" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌬</v>
       </c>
       <c r="H124" t="s">
@@ -15791,25 +16279,29 @@
         <v>8879</v>
       </c>
       <c r="L124" t="str">
+        <f t="shared" si="15"/>
+        <v>⚋⚋⚊𝌀</v>
+      </c>
+      <c r="M124" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌬</v>
+      </c>
+      <c r="N124" t="str">
+        <f t="shared" si="12"/>
+        <v>居</v>
+      </c>
+      <c r="O124" t="str">
         <f t="shared" si="13"/>
-        <v>⚋⚋⚊𝌀</v>
-      </c>
-      <c r="M124" t="str">
-        <f t="shared" si="15"/>
+        <v>𝌬居</v>
+      </c>
+      <c r="P124" t="str">
+        <f t="shared" si="17"/>
         <v>𝌬</v>
       </c>
-      <c r="N124" t="str">
-        <f t="shared" si="11"/>
-        <v>居</v>
-      </c>
-      <c r="O124" t="str">
-        <f t="shared" si="15"/>
-        <v>𝌬</v>
-      </c>
-    </row>
-    <row r="125" spans="2:15">
+    </row>
+    <row r="125" spans="2:16">
       <c r="B125" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D32D</v>
       </c>
       <c r="C125" cm="1">
@@ -15823,7 +16315,7 @@
         <v>40</v>
       </c>
       <c r="F125" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌭</v>
       </c>
       <c r="H125" t="s">
@@ -15851,25 +16343,29 @@
         <v>8887</v>
       </c>
       <c r="L125" t="str">
+        <f t="shared" si="15"/>
+        <v>⚋⚋⚋⚊</v>
+      </c>
+      <c r="M125" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌭</v>
+      </c>
+      <c r="N125" t="str">
+        <f t="shared" si="12"/>
+        <v>法</v>
+      </c>
+      <c r="O125" t="str">
         <f t="shared" si="13"/>
-        <v>⚋⚋⚋⚊</v>
-      </c>
-      <c r="M125" t="str">
-        <f t="shared" si="15"/>
+        <v>𝌭法</v>
+      </c>
+      <c r="P125" t="str">
+        <f t="shared" si="17"/>
         <v>𝌭</v>
       </c>
-      <c r="N125" t="str">
-        <f t="shared" si="11"/>
-        <v>法</v>
-      </c>
-      <c r="O125" t="str">
-        <f t="shared" si="15"/>
-        <v>𝌭</v>
-      </c>
-    </row>
-    <row r="126" spans="2:15">
+    </row>
+    <row r="126" spans="2:16">
       <c r="B126" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D32E</v>
       </c>
       <c r="C126" cm="1">
@@ -15883,7 +16379,7 @@
         <v>41</v>
       </c>
       <c r="F126" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌮</v>
       </c>
       <c r="H126" t="s">
@@ -15911,25 +16407,29 @@
         <v>8888</v>
       </c>
       <c r="L126" t="str">
+        <f t="shared" si="15"/>
+        <v>⚋⚋⚋⚋</v>
+      </c>
+      <c r="M126" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌮</v>
+      </c>
+      <c r="N126" t="str">
+        <f t="shared" si="12"/>
+        <v>應</v>
+      </c>
+      <c r="O126" t="str">
         <f t="shared" si="13"/>
-        <v>⚋⚋⚋⚋</v>
-      </c>
-      <c r="M126" t="str">
-        <f t="shared" si="15"/>
+        <v>𝌮應</v>
+      </c>
+      <c r="P126" t="str">
+        <f t="shared" si="17"/>
         <v>𝌮</v>
       </c>
-      <c r="N126" t="str">
-        <f t="shared" si="11"/>
-        <v>應</v>
-      </c>
-      <c r="O126" t="str">
-        <f t="shared" si="15"/>
-        <v>𝌮</v>
-      </c>
-    </row>
-    <row r="127" spans="2:15">
+    </row>
+    <row r="127" spans="2:16">
       <c r="B127" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D32F</v>
       </c>
       <c r="C127" cm="1">
@@ -15943,7 +16443,7 @@
         <v>42</v>
       </c>
       <c r="F127" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌯</v>
       </c>
       <c r="H127" t="s">
@@ -15971,25 +16471,29 @@
         <v>8889</v>
       </c>
       <c r="L127" t="str">
+        <f t="shared" si="15"/>
+        <v>⚋⚋⚋𝌀</v>
+      </c>
+      <c r="M127" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌯</v>
+      </c>
+      <c r="N127" t="str">
+        <f t="shared" si="12"/>
+        <v>迎</v>
+      </c>
+      <c r="O127" t="str">
         <f t="shared" si="13"/>
-        <v>⚋⚋⚋𝌀</v>
-      </c>
-      <c r="M127" t="str">
-        <f t="shared" si="15"/>
+        <v>𝌯迎</v>
+      </c>
+      <c r="P127" t="str">
+        <f t="shared" si="17"/>
         <v>𝌯</v>
       </c>
-      <c r="N127" t="str">
-        <f t="shared" si="11"/>
-        <v>迎</v>
-      </c>
-      <c r="O127" t="str">
-        <f t="shared" si="15"/>
-        <v>𝌯</v>
-      </c>
-    </row>
-    <row r="128" spans="2:15">
+    </row>
+    <row r="128" spans="2:16">
       <c r="B128" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D330</v>
       </c>
       <c r="C128" cm="1">
@@ -16003,7 +16507,7 @@
         <v>43</v>
       </c>
       <c r="F128" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌰</v>
       </c>
       <c r="H128" t="s">
@@ -16031,25 +16535,29 @@
         <v>8897</v>
       </c>
       <c r="L128" t="str">
+        <f t="shared" si="15"/>
+        <v>⚋⚋𝌀⚊</v>
+      </c>
+      <c r="M128" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌰</v>
+      </c>
+      <c r="N128" t="str">
+        <f t="shared" si="12"/>
+        <v>遇</v>
+      </c>
+      <c r="O128" t="str">
         <f t="shared" si="13"/>
-        <v>⚋⚋𝌀⚊</v>
-      </c>
-      <c r="M128" t="str">
-        <f t="shared" si="15"/>
+        <v>𝌰遇</v>
+      </c>
+      <c r="P128" t="str">
+        <f t="shared" si="17"/>
         <v>𝌰</v>
       </c>
-      <c r="N128" t="str">
-        <f t="shared" si="11"/>
-        <v>遇</v>
-      </c>
-      <c r="O128" t="str">
-        <f t="shared" si="15"/>
-        <v>𝌰</v>
-      </c>
-    </row>
-    <row r="129" spans="2:15">
+    </row>
+    <row r="129" spans="2:16">
       <c r="B129" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D331</v>
       </c>
       <c r="C129" cm="1">
@@ -16063,7 +16571,7 @@
         <v>44</v>
       </c>
       <c r="F129" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌱</v>
       </c>
       <c r="H129" t="s">
@@ -16091,25 +16599,29 @@
         <v>8898</v>
       </c>
       <c r="L129" t="str">
+        <f t="shared" si="15"/>
+        <v>⚋⚋𝌀⚋</v>
+      </c>
+      <c r="M129" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌱</v>
+      </c>
+      <c r="N129" t="str">
+        <f t="shared" si="12"/>
+        <v>竈</v>
+      </c>
+      <c r="O129" t="str">
         <f t="shared" si="13"/>
-        <v>⚋⚋𝌀⚋</v>
-      </c>
-      <c r="M129" t="str">
-        <f t="shared" si="15"/>
+        <v>𝌱竈</v>
+      </c>
+      <c r="P129" t="str">
+        <f t="shared" si="17"/>
         <v>𝌱</v>
       </c>
-      <c r="N129" t="str">
-        <f t="shared" si="11"/>
-        <v>竈</v>
-      </c>
-      <c r="O129" t="str">
-        <f t="shared" si="15"/>
-        <v>𝌱</v>
-      </c>
-    </row>
-    <row r="130" spans="2:15">
+    </row>
+    <row r="130" spans="2:16">
       <c r="B130" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1D332</v>
       </c>
       <c r="C130" cm="1">
@@ -16123,7 +16635,7 @@
         <v>45</v>
       </c>
       <c r="F130" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌲</v>
       </c>
       <c r="H130" t="s">
@@ -16151,25 +16663,29 @@
         <v>8899</v>
       </c>
       <c r="L130" t="str">
+        <f t="shared" si="15"/>
+        <v>⚋⚋𝌀𝌀</v>
+      </c>
+      <c r="M130" t="str">
+        <f t="shared" ref="M130:P145" si="18">_xlfn.UNICHAR($C130)</f>
+        <v>𝌲</v>
+      </c>
+      <c r="N130" t="str">
+        <f t="shared" si="12"/>
+        <v>大</v>
+      </c>
+      <c r="O130" t="str">
         <f t="shared" si="13"/>
-        <v>⚋⚋𝌀𝌀</v>
-      </c>
-      <c r="M130" t="str">
-        <f t="shared" ref="M130:O145" si="16">_xlfn.UNICHAR($C130)</f>
+        <v>𝌲大</v>
+      </c>
+      <c r="P130" t="str">
+        <f t="shared" si="18"/>
         <v>𝌲</v>
       </c>
-      <c r="N130" t="str">
-        <f t="shared" si="11"/>
-        <v>大</v>
-      </c>
-      <c r="O130" t="str">
-        <f t="shared" si="16"/>
-        <v>𝌲</v>
-      </c>
-    </row>
-    <row r="131" spans="2:15">
+    </row>
+    <row r="131" spans="2:16">
       <c r="B131" t="str">
-        <f t="shared" ref="B131:B166" si="17">DEC2HEX($C131)</f>
+        <f t="shared" ref="B131:B166" si="19">DEC2HEX($C131)</f>
         <v>1D333</v>
       </c>
       <c r="C131" cm="1">
@@ -16183,7 +16699,7 @@
         <v>46</v>
       </c>
       <c r="F131" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌳</v>
       </c>
       <c r="H131" t="s">
@@ -16211,25 +16727,29 @@
         <v>8977</v>
       </c>
       <c r="L131" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>⚋𝌀⚊⚊</v>
       </c>
       <c r="M131" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>𝌳</v>
       </c>
       <c r="N131" t="str">
-        <f t="shared" ref="N131:N166" si="18">IF($H131="",$G131,$H131)</f>
+        <f t="shared" ref="N131:N166" si="20">IF($H131="",$G131,$H131)</f>
         <v>廓</v>
       </c>
       <c r="O131" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="O131:O166" si="21">M131&amp;N131</f>
+        <v>𝌳廓</v>
+      </c>
+      <c r="P131" t="str">
+        <f t="shared" si="18"/>
         <v>𝌳</v>
       </c>
     </row>
-    <row r="132" spans="2:15">
+    <row r="132" spans="2:16">
       <c r="B132" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1D334</v>
       </c>
       <c r="C132" cm="1">
@@ -16243,7 +16763,7 @@
         <v>47</v>
       </c>
       <c r="F132" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌴</v>
       </c>
       <c r="H132" t="s">
@@ -16271,25 +16791,29 @@
         <v>8978</v>
       </c>
       <c r="L132" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>⚋𝌀⚊⚋</v>
       </c>
       <c r="M132" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>𝌴</v>
       </c>
       <c r="N132" t="str">
+        <f t="shared" si="20"/>
+        <v>文</v>
+      </c>
+      <c r="O132" t="str">
+        <f t="shared" si="21"/>
+        <v>𝌴文</v>
+      </c>
+      <c r="P132" t="str">
         <f t="shared" si="18"/>
-        <v>文</v>
-      </c>
-      <c r="O132" t="str">
-        <f t="shared" si="16"/>
         <v>𝌴</v>
       </c>
     </row>
-    <row r="133" spans="2:15">
+    <row r="133" spans="2:16">
       <c r="B133" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1D335</v>
       </c>
       <c r="C133" cm="1">
@@ -16303,7 +16827,7 @@
         <v>48</v>
       </c>
       <c r="F133" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌵</v>
       </c>
       <c r="H133" t="s">
@@ -16331,25 +16855,29 @@
         <v>8979</v>
       </c>
       <c r="L133" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>⚋𝌀⚊𝌀</v>
       </c>
       <c r="M133" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>𝌵</v>
       </c>
       <c r="N133" t="str">
+        <f t="shared" si="20"/>
+        <v>禮</v>
+      </c>
+      <c r="O133" t="str">
+        <f t="shared" si="21"/>
+        <v>𝌵禮</v>
+      </c>
+      <c r="P133" t="str">
         <f t="shared" si="18"/>
-        <v>禮</v>
-      </c>
-      <c r="O133" t="str">
-        <f t="shared" si="16"/>
         <v>𝌵</v>
       </c>
     </row>
-    <row r="134" spans="2:15">
+    <row r="134" spans="2:16">
       <c r="B134" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1D336</v>
       </c>
       <c r="C134" cm="1">
@@ -16363,7 +16891,7 @@
         <v>49</v>
       </c>
       <c r="F134" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌶</v>
       </c>
       <c r="H134" t="s">
@@ -16391,25 +16919,29 @@
         <v>8987</v>
       </c>
       <c r="L134" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>⚋𝌀⚋⚊</v>
       </c>
       <c r="M134" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>𝌶</v>
       </c>
       <c r="N134" t="str">
+        <f t="shared" si="20"/>
+        <v>逃</v>
+      </c>
+      <c r="O134" t="str">
+        <f t="shared" si="21"/>
+        <v>𝌶逃</v>
+      </c>
+      <c r="P134" t="str">
         <f t="shared" si="18"/>
-        <v>逃</v>
-      </c>
-      <c r="O134" t="str">
-        <f t="shared" si="16"/>
         <v>𝌶</v>
       </c>
     </row>
-    <row r="135" spans="2:15">
+    <row r="135" spans="2:16">
       <c r="B135" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1D337</v>
       </c>
       <c r="C135" cm="1">
@@ -16423,7 +16955,7 @@
         <v>50</v>
       </c>
       <c r="F135" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌷</v>
       </c>
       <c r="H135" t="s">
@@ -16451,25 +16983,29 @@
         <v>8988</v>
       </c>
       <c r="L135" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>⚋𝌀⚋⚋</v>
       </c>
       <c r="M135" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>𝌷</v>
       </c>
       <c r="N135" t="str">
+        <f t="shared" si="20"/>
+        <v>唐</v>
+      </c>
+      <c r="O135" t="str">
+        <f t="shared" si="21"/>
+        <v>𝌷唐</v>
+      </c>
+      <c r="P135" t="str">
         <f t="shared" si="18"/>
-        <v>唐</v>
-      </c>
-      <c r="O135" t="str">
-        <f t="shared" si="16"/>
         <v>𝌷</v>
       </c>
     </row>
-    <row r="136" spans="2:15">
+    <row r="136" spans="2:16">
       <c r="B136" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1D338</v>
       </c>
       <c r="C136" cm="1">
@@ -16483,7 +17019,7 @@
         <v>51</v>
       </c>
       <c r="F136" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌸</v>
       </c>
       <c r="H136" t="s">
@@ -16511,25 +17047,29 @@
         <v>8989</v>
       </c>
       <c r="L136" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>⚋𝌀⚋𝌀</v>
       </c>
       <c r="M136" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>𝌸</v>
       </c>
       <c r="N136" t="str">
+        <f t="shared" si="20"/>
+        <v>常</v>
+      </c>
+      <c r="O136" t="str">
+        <f t="shared" si="21"/>
+        <v>𝌸常</v>
+      </c>
+      <c r="P136" t="str">
         <f t="shared" si="18"/>
-        <v>常</v>
-      </c>
-      <c r="O136" t="str">
-        <f t="shared" si="16"/>
         <v>𝌸</v>
       </c>
     </row>
-    <row r="137" spans="2:15">
+    <row r="137" spans="2:16">
       <c r="B137" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1D339</v>
       </c>
       <c r="C137" cm="1">
@@ -16543,7 +17083,7 @@
         <v>52</v>
       </c>
       <c r="F137" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌹</v>
       </c>
       <c r="H137" t="s">
@@ -16571,25 +17111,29 @@
         <v>8997</v>
       </c>
       <c r="L137" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>⚋𝌀𝌀⚊</v>
       </c>
       <c r="M137" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>𝌹</v>
       </c>
       <c r="N137" t="str">
+        <f t="shared" si="20"/>
+        <v>度</v>
+      </c>
+      <c r="O137" t="str">
+        <f t="shared" si="21"/>
+        <v>𝌹度</v>
+      </c>
+      <c r="P137" t="str">
         <f t="shared" si="18"/>
-        <v>度</v>
-      </c>
-      <c r="O137" t="str">
-        <f t="shared" si="16"/>
         <v>𝌹</v>
       </c>
     </row>
-    <row r="138" spans="2:15">
+    <row r="138" spans="2:16">
       <c r="B138" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1D33A</v>
       </c>
       <c r="C138" cm="1">
@@ -16603,7 +17147,7 @@
         <v>53</v>
       </c>
       <c r="F138" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌺</v>
       </c>
       <c r="H138" t="s">
@@ -16631,25 +17175,29 @@
         <v>8998</v>
       </c>
       <c r="L138" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>⚋𝌀𝌀⚋</v>
       </c>
       <c r="M138" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>𝌺</v>
       </c>
       <c r="N138" t="str">
+        <f t="shared" si="20"/>
+        <v>永</v>
+      </c>
+      <c r="O138" t="str">
+        <f t="shared" si="21"/>
+        <v>𝌺永</v>
+      </c>
+      <c r="P138" t="str">
         <f t="shared" si="18"/>
-        <v>永</v>
-      </c>
-      <c r="O138" t="str">
-        <f t="shared" si="16"/>
         <v>𝌺</v>
       </c>
     </row>
-    <row r="139" spans="2:15">
+    <row r="139" spans="2:16">
       <c r="B139" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1D33B</v>
       </c>
       <c r="C139" cm="1">
@@ -16663,7 +17211,7 @@
         <v>54</v>
       </c>
       <c r="F139" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌻</v>
       </c>
       <c r="H139" t="s">
@@ -16691,25 +17239,29 @@
         <v>8999</v>
       </c>
       <c r="L139" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>⚋𝌀𝌀𝌀</v>
       </c>
       <c r="M139" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>𝌻</v>
       </c>
       <c r="N139" t="str">
+        <f t="shared" si="20"/>
+        <v>昆</v>
+      </c>
+      <c r="O139" t="str">
+        <f t="shared" si="21"/>
+        <v>𝌻昆</v>
+      </c>
+      <c r="P139" t="str">
         <f t="shared" si="18"/>
-        <v>昆</v>
-      </c>
-      <c r="O139" t="str">
-        <f t="shared" si="16"/>
         <v>𝌻</v>
       </c>
     </row>
-    <row r="140" spans="2:15">
+    <row r="140" spans="2:16">
       <c r="B140" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1D33C</v>
       </c>
       <c r="C140" cm="1">
@@ -16723,7 +17275,7 @@
         <v>55</v>
       </c>
       <c r="F140" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌼</v>
       </c>
       <c r="H140" t="s">
@@ -16751,25 +17303,29 @@
         <v>9777</v>
       </c>
       <c r="L140" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>𝌀⚊⚊⚊</v>
       </c>
       <c r="M140" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>𝌼</v>
       </c>
       <c r="N140" t="str">
+        <f t="shared" si="20"/>
+        <v>減</v>
+      </c>
+      <c r="O140" t="str">
+        <f t="shared" si="21"/>
+        <v>𝌼減</v>
+      </c>
+      <c r="P140" t="str">
         <f t="shared" si="18"/>
-        <v>減</v>
-      </c>
-      <c r="O140" t="str">
-        <f t="shared" si="16"/>
         <v>𝌼</v>
       </c>
     </row>
-    <row r="141" spans="2:15">
+    <row r="141" spans="2:16">
       <c r="B141" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1D33D</v>
       </c>
       <c r="C141" cm="1">
@@ -16783,7 +17339,7 @@
         <v>56</v>
       </c>
       <c r="F141" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌽</v>
       </c>
       <c r="H141" t="s">
@@ -16811,25 +17367,29 @@
         <v>9778</v>
       </c>
       <c r="L141" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>𝌀⚊⚊⚋</v>
       </c>
       <c r="M141" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>𝌽</v>
       </c>
       <c r="N141" t="str">
+        <f t="shared" si="20"/>
+        <v>唫</v>
+      </c>
+      <c r="O141" t="str">
+        <f t="shared" si="21"/>
+        <v>𝌽唫</v>
+      </c>
+      <c r="P141" t="str">
         <f t="shared" si="18"/>
-        <v>唫</v>
-      </c>
-      <c r="O141" t="str">
-        <f t="shared" si="16"/>
         <v>𝌽</v>
       </c>
     </row>
-    <row r="142" spans="2:15">
+    <row r="142" spans="2:16">
       <c r="B142" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1D33E</v>
       </c>
       <c r="C142" cm="1">
@@ -16843,7 +17403,7 @@
         <v>57</v>
       </c>
       <c r="F142" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌾</v>
       </c>
       <c r="H142" t="s">
@@ -16871,25 +17431,29 @@
         <v>9779</v>
       </c>
       <c r="L142" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>𝌀⚊⚊𝌀</v>
       </c>
       <c r="M142" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>𝌾</v>
       </c>
       <c r="N142" t="str">
+        <f t="shared" si="20"/>
+        <v>守</v>
+      </c>
+      <c r="O142" t="str">
+        <f t="shared" si="21"/>
+        <v>𝌾守</v>
+      </c>
+      <c r="P142" t="str">
         <f t="shared" si="18"/>
-        <v>守</v>
-      </c>
-      <c r="O142" t="str">
-        <f t="shared" si="16"/>
         <v>𝌾</v>
       </c>
     </row>
-    <row r="143" spans="2:15">
+    <row r="143" spans="2:16">
       <c r="B143" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1D33F</v>
       </c>
       <c r="C143" cm="1">
@@ -16903,7 +17467,7 @@
         <v>58</v>
       </c>
       <c r="F143" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝌿</v>
       </c>
       <c r="H143" t="s">
@@ -16931,25 +17495,29 @@
         <v>9787</v>
       </c>
       <c r="L143" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>𝌀⚊⚋⚊</v>
       </c>
       <c r="M143" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>𝌿</v>
       </c>
       <c r="N143" t="str">
+        <f t="shared" si="20"/>
+        <v>翕</v>
+      </c>
+      <c r="O143" t="str">
+        <f t="shared" si="21"/>
+        <v>𝌿翕</v>
+      </c>
+      <c r="P143" t="str">
         <f t="shared" si="18"/>
-        <v>翕</v>
-      </c>
-      <c r="O143" t="str">
-        <f t="shared" si="16"/>
         <v>𝌿</v>
       </c>
     </row>
-    <row r="144" spans="2:15">
+    <row r="144" spans="2:16">
       <c r="B144" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1D340</v>
       </c>
       <c r="C144" cm="1">
@@ -16963,7 +17531,7 @@
         <v>59</v>
       </c>
       <c r="F144" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝍀</v>
       </c>
       <c r="H144" t="s">
@@ -16991,25 +17559,29 @@
         <v>9788</v>
       </c>
       <c r="L144" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>𝌀⚊⚋⚋</v>
       </c>
       <c r="M144" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>𝍀</v>
       </c>
       <c r="N144" t="str">
+        <f t="shared" si="20"/>
+        <v>聚</v>
+      </c>
+      <c r="O144" t="str">
+        <f t="shared" si="21"/>
+        <v>𝍀聚</v>
+      </c>
+      <c r="P144" t="str">
         <f t="shared" si="18"/>
-        <v>聚</v>
-      </c>
-      <c r="O144" t="str">
-        <f t="shared" si="16"/>
         <v>𝍀</v>
       </c>
     </row>
-    <row r="145" spans="2:15">
+    <row r="145" spans="2:16">
       <c r="B145" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1D341</v>
       </c>
       <c r="C145" cm="1">
@@ -17023,7 +17595,7 @@
         <v>60</v>
       </c>
       <c r="F145" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝍁</v>
       </c>
       <c r="H145" t="s">
@@ -17051,25 +17623,29 @@
         <v>9789</v>
       </c>
       <c r="L145" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>𝌀⚊⚋𝌀</v>
       </c>
       <c r="M145" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>𝍁</v>
       </c>
       <c r="N145" t="str">
+        <f t="shared" si="20"/>
+        <v>積</v>
+      </c>
+      <c r="O145" t="str">
+        <f t="shared" si="21"/>
+        <v>𝍁積</v>
+      </c>
+      <c r="P145" t="str">
         <f t="shared" si="18"/>
-        <v>積</v>
-      </c>
-      <c r="O145" t="str">
-        <f t="shared" si="16"/>
         <v>𝍁</v>
       </c>
     </row>
-    <row r="146" spans="2:15">
+    <row r="146" spans="2:16">
       <c r="B146" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1D342</v>
       </c>
       <c r="C146" cm="1">
@@ -17083,7 +17659,7 @@
         <v>61</v>
       </c>
       <c r="F146" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝍂</v>
       </c>
       <c r="H146" t="s">
@@ -17111,25 +17687,29 @@
         <v>9797</v>
       </c>
       <c r="L146" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>𝌀⚊𝌀⚊</v>
       </c>
       <c r="M146" t="str">
-        <f t="shared" ref="M146:O161" si="19">_xlfn.UNICHAR($C146)</f>
+        <f t="shared" ref="M146:P161" si="22">_xlfn.UNICHAR($C146)</f>
         <v>𝍂</v>
       </c>
       <c r="N146" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>飾</v>
       </c>
       <c r="O146" t="str">
+        <f t="shared" si="21"/>
+        <v>𝍂飾</v>
+      </c>
+      <c r="P146" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍂</v>
+      </c>
+    </row>
+    <row r="147" spans="2:16">
+      <c r="B147" t="str">
         <f t="shared" si="19"/>
-        <v>𝍂</v>
-      </c>
-    </row>
-    <row r="147" spans="2:15">
-      <c r="B147" t="str">
-        <f t="shared" si="17"/>
         <v>1D343</v>
       </c>
       <c r="C147" cm="1">
@@ -17143,7 +17723,7 @@
         <v>62</v>
       </c>
       <c r="F147" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝍃</v>
       </c>
       <c r="H147" t="s">
@@ -17171,25 +17751,29 @@
         <v>9798</v>
       </c>
       <c r="L147" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>𝌀⚊𝌀⚋</v>
       </c>
       <c r="M147" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍃</v>
+      </c>
+      <c r="N147" t="str">
+        <f t="shared" si="20"/>
+        <v>疑</v>
+      </c>
+      <c r="O147" t="str">
+        <f t="shared" si="21"/>
+        <v>𝍃疑</v>
+      </c>
+      <c r="P147" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍃</v>
+      </c>
+    </row>
+    <row r="148" spans="2:16">
+      <c r="B148" t="str">
         <f t="shared" si="19"/>
-        <v>𝍃</v>
-      </c>
-      <c r="N147" t="str">
-        <f t="shared" si="18"/>
-        <v>疑</v>
-      </c>
-      <c r="O147" t="str">
-        <f t="shared" si="19"/>
-        <v>𝍃</v>
-      </c>
-    </row>
-    <row r="148" spans="2:15">
-      <c r="B148" t="str">
-        <f t="shared" si="17"/>
         <v>1D344</v>
       </c>
       <c r="C148" cm="1">
@@ -17203,7 +17787,7 @@
         <v>63</v>
       </c>
       <c r="F148" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝍄</v>
       </c>
       <c r="H148" t="s">
@@ -17231,25 +17815,29 @@
         <v>9799</v>
       </c>
       <c r="L148" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>𝌀⚊𝌀𝌀</v>
       </c>
       <c r="M148" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍄</v>
+      </c>
+      <c r="N148" t="str">
+        <f t="shared" si="20"/>
+        <v>視</v>
+      </c>
+      <c r="O148" t="str">
+        <f t="shared" si="21"/>
+        <v>𝍄視</v>
+      </c>
+      <c r="P148" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍄</v>
+      </c>
+    </row>
+    <row r="149" spans="2:16">
+      <c r="B149" t="str">
         <f t="shared" si="19"/>
-        <v>𝍄</v>
-      </c>
-      <c r="N148" t="str">
-        <f t="shared" si="18"/>
-        <v>視</v>
-      </c>
-      <c r="O148" t="str">
-        <f t="shared" si="19"/>
-        <v>𝍄</v>
-      </c>
-    </row>
-    <row r="149" spans="2:15">
-      <c r="B149" t="str">
-        <f t="shared" si="17"/>
         <v>1D345</v>
       </c>
       <c r="C149" cm="1">
@@ -17263,7 +17851,7 @@
         <v>64</v>
       </c>
       <c r="F149" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝍅</v>
       </c>
       <c r="H149" t="s">
@@ -17291,25 +17879,29 @@
         <v>9877</v>
       </c>
       <c r="L149" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>𝌀⚋⚊⚊</v>
       </c>
       <c r="M149" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍅</v>
+      </c>
+      <c r="N149" t="str">
+        <f t="shared" si="20"/>
+        <v>沈</v>
+      </c>
+      <c r="O149" t="str">
+        <f t="shared" si="21"/>
+        <v>𝍅沈</v>
+      </c>
+      <c r="P149" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍅</v>
+      </c>
+    </row>
+    <row r="150" spans="2:16">
+      <c r="B150" t="str">
         <f t="shared" si="19"/>
-        <v>𝍅</v>
-      </c>
-      <c r="N149" t="str">
-        <f t="shared" si="18"/>
-        <v>沈</v>
-      </c>
-      <c r="O149" t="str">
-        <f t="shared" si="19"/>
-        <v>𝍅</v>
-      </c>
-    </row>
-    <row r="150" spans="2:15">
-      <c r="B150" t="str">
-        <f t="shared" si="17"/>
         <v>1D346</v>
       </c>
       <c r="C150" cm="1">
@@ -17323,7 +17915,7 @@
         <v>65</v>
       </c>
       <c r="F150" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝍆</v>
       </c>
       <c r="H150" t="s">
@@ -17351,25 +17943,29 @@
         <v>9878</v>
       </c>
       <c r="L150" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>𝌀⚋⚊⚋</v>
       </c>
       <c r="M150" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍆</v>
+      </c>
+      <c r="N150" t="str">
+        <f t="shared" si="20"/>
+        <v>內</v>
+      </c>
+      <c r="O150" t="str">
+        <f t="shared" si="21"/>
+        <v>𝍆內</v>
+      </c>
+      <c r="P150" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍆</v>
+      </c>
+    </row>
+    <row r="151" spans="2:16">
+      <c r="B151" t="str">
         <f t="shared" si="19"/>
-        <v>𝍆</v>
-      </c>
-      <c r="N150" t="str">
-        <f t="shared" si="18"/>
-        <v>內</v>
-      </c>
-      <c r="O150" t="str">
-        <f t="shared" si="19"/>
-        <v>𝍆</v>
-      </c>
-    </row>
-    <row r="151" spans="2:15">
-      <c r="B151" t="str">
-        <f t="shared" si="17"/>
         <v>1D347</v>
       </c>
       <c r="C151" cm="1">
@@ -17383,7 +17979,7 @@
         <v>66</v>
       </c>
       <c r="F151" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝍇</v>
       </c>
       <c r="H151" t="s">
@@ -17411,25 +18007,29 @@
         <v>9879</v>
       </c>
       <c r="L151" t="str">
-        <f t="shared" ref="L151:L166" si="20">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TEXT($J151,"0"),"1","⚊"),"2","⚋"),"3","𝌀")</f>
+        <f t="shared" ref="L151:L166" si="23">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TEXT($J151,"0"),"1","⚊"),"2","⚋"),"3","𝌀")</f>
         <v>𝌀⚋⚊𝌀</v>
       </c>
       <c r="M151" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍇</v>
+      </c>
+      <c r="N151" t="str">
+        <f t="shared" si="20"/>
+        <v>去</v>
+      </c>
+      <c r="O151" t="str">
+        <f t="shared" si="21"/>
+        <v>𝍇去</v>
+      </c>
+      <c r="P151" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍇</v>
+      </c>
+    </row>
+    <row r="152" spans="2:16">
+      <c r="B152" t="str">
         <f t="shared" si="19"/>
-        <v>𝍇</v>
-      </c>
-      <c r="N151" t="str">
-        <f t="shared" si="18"/>
-        <v>去</v>
-      </c>
-      <c r="O151" t="str">
-        <f t="shared" si="19"/>
-        <v>𝍇</v>
-      </c>
-    </row>
-    <row r="152" spans="2:15">
-      <c r="B152" t="str">
-        <f t="shared" si="17"/>
         <v>1D348</v>
       </c>
       <c r="C152" cm="1">
@@ -17443,7 +18043,7 @@
         <v>67</v>
       </c>
       <c r="F152" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝍈</v>
       </c>
       <c r="H152" t="s">
@@ -17471,25 +18071,29 @@
         <v>9887</v>
       </c>
       <c r="L152" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌀⚋⚋⚊</v>
+      </c>
+      <c r="M152" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍈</v>
+      </c>
+      <c r="N152" t="str">
         <f t="shared" si="20"/>
-        <v>𝌀⚋⚋⚊</v>
-      </c>
-      <c r="M152" t="str">
+        <v>晦</v>
+      </c>
+      <c r="O152" t="str">
+        <f t="shared" si="21"/>
+        <v>𝍈晦</v>
+      </c>
+      <c r="P152" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍈</v>
+      </c>
+    </row>
+    <row r="153" spans="2:16">
+      <c r="B153" t="str">
         <f t="shared" si="19"/>
-        <v>𝍈</v>
-      </c>
-      <c r="N152" t="str">
-        <f t="shared" si="18"/>
-        <v>晦</v>
-      </c>
-      <c r="O152" t="str">
-        <f t="shared" si="19"/>
-        <v>𝍈</v>
-      </c>
-    </row>
-    <row r="153" spans="2:15">
-      <c r="B153" t="str">
-        <f t="shared" si="17"/>
         <v>1D349</v>
       </c>
       <c r="C153" cm="1">
@@ -17503,7 +18107,7 @@
         <v>68</v>
       </c>
       <c r="F153" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝍉</v>
       </c>
       <c r="H153" t="s">
@@ -17531,25 +18135,29 @@
         <v>9888</v>
       </c>
       <c r="L153" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌀⚋⚋⚋</v>
+      </c>
+      <c r="M153" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍉</v>
+      </c>
+      <c r="N153" t="str">
         <f t="shared" si="20"/>
-        <v>𝌀⚋⚋⚋</v>
-      </c>
-      <c r="M153" t="str">
+        <v>瞢</v>
+      </c>
+      <c r="O153" t="str">
+        <f t="shared" si="21"/>
+        <v>𝍉瞢</v>
+      </c>
+      <c r="P153" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍉</v>
+      </c>
+    </row>
+    <row r="154" spans="2:16">
+      <c r="B154" t="str">
         <f t="shared" si="19"/>
-        <v>𝍉</v>
-      </c>
-      <c r="N153" t="str">
-        <f t="shared" si="18"/>
-        <v>瞢</v>
-      </c>
-      <c r="O153" t="str">
-        <f t="shared" si="19"/>
-        <v>𝍉</v>
-      </c>
-    </row>
-    <row r="154" spans="2:15">
-      <c r="B154" t="str">
-        <f t="shared" si="17"/>
         <v>1D34A</v>
       </c>
       <c r="C154" cm="1">
@@ -17563,7 +18171,7 @@
         <v>69</v>
       </c>
       <c r="F154" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝍊</v>
       </c>
       <c r="H154" t="s">
@@ -17591,25 +18199,29 @@
         <v>9889</v>
       </c>
       <c r="L154" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌀⚋⚋𝌀</v>
+      </c>
+      <c r="M154" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍊</v>
+      </c>
+      <c r="N154" t="str">
         <f t="shared" si="20"/>
-        <v>𝌀⚋⚋𝌀</v>
-      </c>
-      <c r="M154" t="str">
+        <v>窮</v>
+      </c>
+      <c r="O154" t="str">
+        <f t="shared" si="21"/>
+        <v>𝍊窮</v>
+      </c>
+      <c r="P154" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍊</v>
+      </c>
+    </row>
+    <row r="155" spans="2:16">
+      <c r="B155" t="str">
         <f t="shared" si="19"/>
-        <v>𝍊</v>
-      </c>
-      <c r="N154" t="str">
-        <f t="shared" si="18"/>
-        <v>窮</v>
-      </c>
-      <c r="O154" t="str">
-        <f t="shared" si="19"/>
-        <v>𝍊</v>
-      </c>
-    </row>
-    <row r="155" spans="2:15">
-      <c r="B155" t="str">
-        <f t="shared" si="17"/>
         <v>1D34B</v>
       </c>
       <c r="C155" cm="1">
@@ -17623,7 +18235,7 @@
         <v>70</v>
       </c>
       <c r="F155" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝍋</v>
       </c>
       <c r="H155" t="s">
@@ -17651,25 +18263,29 @@
         <v>9897</v>
       </c>
       <c r="L155" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌀⚋𝌀⚊</v>
+      </c>
+      <c r="M155" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍋</v>
+      </c>
+      <c r="N155" t="str">
         <f t="shared" si="20"/>
-        <v>𝌀⚋𝌀⚊</v>
-      </c>
-      <c r="M155" t="str">
+        <v>割</v>
+      </c>
+      <c r="O155" t="str">
+        <f t="shared" si="21"/>
+        <v>𝍋割</v>
+      </c>
+      <c r="P155" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍋</v>
+      </c>
+    </row>
+    <row r="156" spans="2:16">
+      <c r="B156" t="str">
         <f t="shared" si="19"/>
-        <v>𝍋</v>
-      </c>
-      <c r="N155" t="str">
-        <f t="shared" si="18"/>
-        <v>割</v>
-      </c>
-      <c r="O155" t="str">
-        <f t="shared" si="19"/>
-        <v>𝍋</v>
-      </c>
-    </row>
-    <row r="156" spans="2:15">
-      <c r="B156" t="str">
-        <f t="shared" si="17"/>
         <v>1D34C</v>
       </c>
       <c r="C156" cm="1">
@@ -17683,7 +18299,7 @@
         <v>71</v>
       </c>
       <c r="F156" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝍌</v>
       </c>
       <c r="H156" t="s">
@@ -17711,25 +18327,29 @@
         <v>9898</v>
       </c>
       <c r="L156" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌀⚋𝌀⚋</v>
+      </c>
+      <c r="M156" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍌</v>
+      </c>
+      <c r="N156" t="str">
         <f t="shared" si="20"/>
-        <v>𝌀⚋𝌀⚋</v>
-      </c>
-      <c r="M156" t="str">
+        <v>止</v>
+      </c>
+      <c r="O156" t="str">
+        <f t="shared" si="21"/>
+        <v>𝍌止</v>
+      </c>
+      <c r="P156" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍌</v>
+      </c>
+    </row>
+    <row r="157" spans="2:16">
+      <c r="B157" t="str">
         <f t="shared" si="19"/>
-        <v>𝍌</v>
-      </c>
-      <c r="N156" t="str">
-        <f t="shared" si="18"/>
-        <v>止</v>
-      </c>
-      <c r="O156" t="str">
-        <f t="shared" si="19"/>
-        <v>𝍌</v>
-      </c>
-    </row>
-    <row r="157" spans="2:15">
-      <c r="B157" t="str">
-        <f t="shared" si="17"/>
         <v>1D34D</v>
       </c>
       <c r="C157" cm="1">
@@ -17743,7 +18363,7 @@
         <v>72</v>
       </c>
       <c r="F157" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝍍</v>
       </c>
       <c r="H157" t="s">
@@ -17771,25 +18391,29 @@
         <v>9899</v>
       </c>
       <c r="L157" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌀⚋𝌀𝌀</v>
+      </c>
+      <c r="M157" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍍</v>
+      </c>
+      <c r="N157" t="str">
         <f t="shared" si="20"/>
-        <v>𝌀⚋𝌀𝌀</v>
-      </c>
-      <c r="M157" t="str">
+        <v>堅</v>
+      </c>
+      <c r="O157" t="str">
+        <f t="shared" si="21"/>
+        <v>𝍍堅</v>
+      </c>
+      <c r="P157" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍍</v>
+      </c>
+    </row>
+    <row r="158" spans="2:16">
+      <c r="B158" t="str">
         <f t="shared" si="19"/>
-        <v>𝍍</v>
-      </c>
-      <c r="N157" t="str">
-        <f t="shared" si="18"/>
-        <v>堅</v>
-      </c>
-      <c r="O157" t="str">
-        <f t="shared" si="19"/>
-        <v>𝍍</v>
-      </c>
-    </row>
-    <row r="158" spans="2:15">
-      <c r="B158" t="str">
-        <f t="shared" si="17"/>
         <v>1D34E</v>
       </c>
       <c r="C158" cm="1">
@@ -17803,7 +18427,7 @@
         <v>73</v>
       </c>
       <c r="F158" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝍎</v>
       </c>
       <c r="H158" t="s">
@@ -17831,25 +18455,29 @@
         <v>9977</v>
       </c>
       <c r="L158" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌀𝌀⚊⚊</v>
+      </c>
+      <c r="M158" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍎</v>
+      </c>
+      <c r="N158" t="str">
         <f t="shared" si="20"/>
-        <v>𝌀𝌀⚊⚊</v>
-      </c>
-      <c r="M158" t="str">
+        <v>成</v>
+      </c>
+      <c r="O158" t="str">
+        <f t="shared" si="21"/>
+        <v>𝍎成</v>
+      </c>
+      <c r="P158" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍎</v>
+      </c>
+    </row>
+    <row r="159" spans="2:16">
+      <c r="B159" t="str">
         <f t="shared" si="19"/>
-        <v>𝍎</v>
-      </c>
-      <c r="N158" t="str">
-        <f t="shared" si="18"/>
-        <v>成</v>
-      </c>
-      <c r="O158" t="str">
-        <f t="shared" si="19"/>
-        <v>𝍎</v>
-      </c>
-    </row>
-    <row r="159" spans="2:15">
-      <c r="B159" t="str">
-        <f t="shared" si="17"/>
         <v>1D34F</v>
       </c>
       <c r="C159" cm="1">
@@ -17863,7 +18491,7 @@
         <v>74</v>
       </c>
       <c r="F159" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝍏</v>
       </c>
       <c r="H159" t="s">
@@ -17891,25 +18519,29 @@
         <v>9978</v>
       </c>
       <c r="L159" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌀𝌀⚊⚋</v>
+      </c>
+      <c r="M159" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍏</v>
+      </c>
+      <c r="N159" t="str">
         <f t="shared" si="20"/>
-        <v>𝌀𝌀⚊⚋</v>
-      </c>
-      <c r="M159" t="str">
+        <v>䦯</v>
+      </c>
+      <c r="O159" t="str">
+        <f t="shared" si="21"/>
+        <v>𝍏䦯</v>
+      </c>
+      <c r="P159" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍏</v>
+      </c>
+    </row>
+    <row r="160" spans="2:16">
+      <c r="B160" t="str">
         <f t="shared" si="19"/>
-        <v>𝍏</v>
-      </c>
-      <c r="N159" t="str">
-        <f t="shared" si="18"/>
-        <v>䦯</v>
-      </c>
-      <c r="O159" t="str">
-        <f t="shared" si="19"/>
-        <v>𝍏</v>
-      </c>
-    </row>
-    <row r="160" spans="2:15">
-      <c r="B160" t="str">
-        <f t="shared" si="17"/>
         <v>1D350</v>
       </c>
       <c r="C160" cm="1">
@@ -17923,7 +18555,7 @@
         <v>75</v>
       </c>
       <c r="F160" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝍐</v>
       </c>
       <c r="H160" t="s">
@@ -17951,25 +18583,29 @@
         <v>9979</v>
       </c>
       <c r="L160" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌀𝌀⚊𝌀</v>
+      </c>
+      <c r="M160" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍐</v>
+      </c>
+      <c r="N160" t="str">
         <f t="shared" si="20"/>
-        <v>𝌀𝌀⚊𝌀</v>
-      </c>
-      <c r="M160" t="str">
+        <v>失</v>
+      </c>
+      <c r="O160" t="str">
+        <f t="shared" si="21"/>
+        <v>𝍐失</v>
+      </c>
+      <c r="P160" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍐</v>
+      </c>
+    </row>
+    <row r="161" spans="2:16">
+      <c r="B161" t="str">
         <f t="shared" si="19"/>
-        <v>𝍐</v>
-      </c>
-      <c r="N160" t="str">
-        <f t="shared" si="18"/>
-        <v>失</v>
-      </c>
-      <c r="O160" t="str">
-        <f t="shared" si="19"/>
-        <v>𝍐</v>
-      </c>
-    </row>
-    <row r="161" spans="2:15">
-      <c r="B161" t="str">
-        <f t="shared" si="17"/>
         <v>1D351</v>
       </c>
       <c r="C161" cm="1">
@@ -17983,7 +18619,7 @@
         <v>76</v>
       </c>
       <c r="F161" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝍑</v>
       </c>
       <c r="H161" t="s">
@@ -18011,25 +18647,29 @@
         <v>9987</v>
       </c>
       <c r="L161" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌀𝌀⚋⚊</v>
+      </c>
+      <c r="M161" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍑</v>
+      </c>
+      <c r="N161" t="str">
         <f t="shared" si="20"/>
-        <v>𝌀𝌀⚋⚊</v>
-      </c>
-      <c r="M161" t="str">
+        <v>劇</v>
+      </c>
+      <c r="O161" t="str">
+        <f t="shared" si="21"/>
+        <v>𝍑劇</v>
+      </c>
+      <c r="P161" t="str">
+        <f t="shared" si="22"/>
+        <v>𝍑</v>
+      </c>
+    </row>
+    <row r="162" spans="2:16">
+      <c r="B162" t="str">
         <f t="shared" si="19"/>
-        <v>𝍑</v>
-      </c>
-      <c r="N161" t="str">
-        <f t="shared" si="18"/>
-        <v>劇</v>
-      </c>
-      <c r="O161" t="str">
-        <f t="shared" si="19"/>
-        <v>𝍑</v>
-      </c>
-    </row>
-    <row r="162" spans="2:15">
-      <c r="B162" t="str">
-        <f t="shared" si="17"/>
         <v>1D352</v>
       </c>
       <c r="C162" cm="1">
@@ -18043,7 +18683,7 @@
         <v>77</v>
       </c>
       <c r="F162" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝍒</v>
       </c>
       <c r="H162" t="s">
@@ -18071,25 +18711,29 @@
         <v>9988</v>
       </c>
       <c r="L162" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌀𝌀⚋⚋</v>
+      </c>
+      <c r="M162" t="str">
+        <f t="shared" ref="M162:P166" si="24">_xlfn.UNICHAR($C162)</f>
+        <v>𝍒</v>
+      </c>
+      <c r="N162" t="str">
         <f t="shared" si="20"/>
-        <v>𝌀𝌀⚋⚋</v>
-      </c>
-      <c r="M162" t="str">
-        <f t="shared" ref="M162:O166" si="21">_xlfn.UNICHAR($C162)</f>
-        <v>𝍒</v>
-      </c>
-      <c r="N162" t="str">
-        <f t="shared" si="18"/>
         <v>馴</v>
       </c>
       <c r="O162" t="str">
         <f t="shared" si="21"/>
+        <v>𝍒馴</v>
+      </c>
+      <c r="P162" t="str">
+        <f t="shared" si="24"/>
         <v>𝍒</v>
       </c>
     </row>
-    <row r="163" spans="2:15">
+    <row r="163" spans="2:16">
       <c r="B163" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1D353</v>
       </c>
       <c r="C163" cm="1">
@@ -18103,7 +18747,7 @@
         <v>78</v>
       </c>
       <c r="F163" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝍓</v>
       </c>
       <c r="H163" t="s">
@@ -18131,25 +18775,29 @@
         <v>9989</v>
       </c>
       <c r="L163" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌀𝌀⚋𝌀</v>
+      </c>
+      <c r="M163" t="str">
+        <f t="shared" si="24"/>
+        <v>𝍓</v>
+      </c>
+      <c r="N163" t="str">
         <f t="shared" si="20"/>
-        <v>𝌀𝌀⚋𝌀</v>
-      </c>
-      <c r="M163" t="str">
-        <f t="shared" si="21"/>
-        <v>𝍓</v>
-      </c>
-      <c r="N163" t="str">
-        <f t="shared" si="18"/>
         <v>將</v>
       </c>
       <c r="O163" t="str">
         <f t="shared" si="21"/>
+        <v>𝍓將</v>
+      </c>
+      <c r="P163" t="str">
+        <f t="shared" si="24"/>
         <v>𝍓</v>
       </c>
     </row>
-    <row r="164" spans="2:15">
+    <row r="164" spans="2:16">
       <c r="B164" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1D354</v>
       </c>
       <c r="C164" cm="1">
@@ -18163,7 +18811,7 @@
         <v>79</v>
       </c>
       <c r="F164" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝍔</v>
       </c>
       <c r="H164" t="s">
@@ -18191,25 +18839,29 @@
         <v>9997</v>
       </c>
       <c r="L164" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌀𝌀𝌀⚊</v>
+      </c>
+      <c r="M164" t="str">
+        <f t="shared" si="24"/>
+        <v>𝍔</v>
+      </c>
+      <c r="N164" t="str">
         <f t="shared" si="20"/>
-        <v>𝌀𝌀𝌀⚊</v>
-      </c>
-      <c r="M164" t="str">
-        <f t="shared" si="21"/>
-        <v>𝍔</v>
-      </c>
-      <c r="N164" t="str">
-        <f t="shared" si="18"/>
         <v>難</v>
       </c>
       <c r="O164" t="str">
         <f t="shared" si="21"/>
+        <v>𝍔難</v>
+      </c>
+      <c r="P164" t="str">
+        <f t="shared" si="24"/>
         <v>𝍔</v>
       </c>
     </row>
-    <row r="165" spans="2:15">
+    <row r="165" spans="2:16">
       <c r="B165" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1D355</v>
       </c>
       <c r="C165" cm="1">
@@ -18223,7 +18875,7 @@
         <v>80</v>
       </c>
       <c r="F165" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝍕</v>
       </c>
       <c r="H165" t="s">
@@ -18251,25 +18903,29 @@
         <v>9998</v>
       </c>
       <c r="L165" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌀𝌀𝌀⚋</v>
+      </c>
+      <c r="M165" t="str">
+        <f t="shared" si="24"/>
+        <v>𝍕</v>
+      </c>
+      <c r="N165" t="str">
         <f t="shared" si="20"/>
-        <v>𝌀𝌀𝌀⚋</v>
-      </c>
-      <c r="M165" t="str">
-        <f t="shared" si="21"/>
-        <v>𝍕</v>
-      </c>
-      <c r="N165" t="str">
-        <f t="shared" si="18"/>
         <v>勤</v>
       </c>
       <c r="O165" t="str">
         <f t="shared" si="21"/>
+        <v>𝍕勤</v>
+      </c>
+      <c r="P165" t="str">
+        <f t="shared" si="24"/>
         <v>𝍕</v>
       </c>
     </row>
-    <row r="166" spans="2:15">
+    <row r="166" spans="2:16">
       <c r="B166" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1D356</v>
       </c>
       <c r="C166" cm="1">
@@ -18283,7 +18939,7 @@
         <v>81</v>
       </c>
       <c r="F166" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>𝍖</v>
       </c>
       <c r="H166" t="s">
@@ -18311,19 +18967,23 @@
         <v>9999</v>
       </c>
       <c r="L166" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌀𝌀𝌀𝌀</v>
+      </c>
+      <c r="M166" t="str">
+        <f t="shared" si="24"/>
+        <v>𝍖</v>
+      </c>
+      <c r="N166" t="str">
         <f t="shared" si="20"/>
-        <v>𝌀𝌀𝌀𝌀</v>
-      </c>
-      <c r="M166" t="str">
-        <f t="shared" si="21"/>
-        <v>𝍖</v>
-      </c>
-      <c r="N166" t="str">
-        <f t="shared" si="18"/>
         <v>養</v>
       </c>
       <c r="O166" t="str">
         <f t="shared" si="21"/>
+        <v>𝍖養</v>
+      </c>
+      <c r="P166" t="str">
+        <f t="shared" si="24"/>
         <v>𝍖</v>
       </c>
     </row>
@@ -23143,7 +23803,7 @@
         <v>1069</v>
       </c>
       <c r="L4" t="str">
-        <f t="shared" ref="L4:L11" si="0">"    - xform/"&amp;$E4&amp;"/"&amp;$K4&amp;"/"</f>
+        <f t="shared" ref="L4" si="0">"    - xform/"&amp;$E4&amp;"/"&amp;$K4&amp;"/"</f>
         <v xml:space="preserve">    - xform/𝌅/𝌀𝌀/</v>
       </c>
       <c r="M4" t="str">
@@ -23171,7 +23831,7 @@
         <v>209</v>
       </c>
       <c r="L6" t="str">
-        <f t="shared" ref="L6:L12" si="2">"    - derive/"&amp;$K6&amp;"/"&amp;$G6&amp;"/"</f>
+        <f t="shared" ref="L6:L11" si="2">"    - derive/"&amp;$K6&amp;"/"&amp;$G6&amp;"/"</f>
         <v xml:space="preserve">    - derive/⚊/五/</v>
       </c>
     </row>
